--- a/outputs/relic_terms_table/遺物詞條對照表.xlsx
+++ b/outputs/relic_terms_table/遺物詞條對照表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\games\ERN_relics_helper\outputs\relic_terms_table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9B5EEB-96F2-4F1B-B2DC-AC92FC3F902B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706C925F-6198-4BCE-91A9-AB4A1629A4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>生命力＋３</t>
   </si>
   <si>
-    <t>提升血量上限</t>
-  </si>
-  <si>
     <t>相同詞條不可疊加</t>
   </si>
   <si>
@@ -61,9 +58,6 @@
     <t>集中力＋３</t>
   </si>
   <si>
-    <t>提升專注值上限</t>
-  </si>
-  <si>
     <t>耐力＋１</t>
   </si>
   <si>
@@ -130,15 +124,6 @@
     <t>縮短技藝的冷卻時間＋３</t>
   </si>
   <si>
-    <t>自然累積絕招量表＋１</t>
-  </si>
-  <si>
-    <t>自然累積絕招量表＋２</t>
-  </si>
-  <si>
-    <t>自然累積絕招量表＋３</t>
-  </si>
-  <si>
     <t>強韌度＋１</t>
   </si>
   <si>
@@ -148,9 +133,6 @@
     <t>強韌度＋３</t>
   </si>
   <si>
-    <t>持續恢復血量</t>
-  </si>
-  <si>
     <t>提升物理攻擊力</t>
   </si>
   <si>
@@ -284,9 +266,6 @@
   </si>
   <si>
     <t>提升對發狂的抵抗力</t>
-  </si>
-  <si>
-    <t>受到損傷的當下，能通過攻擊恢復部分血量</t>
   </si>
   <si>
     <t>不同級別可疊加
@@ -308,9 +287,6 @@
     <t>使用聖盃瓶時，連同恢復周圍我方人物</t>
   </si>
   <si>
-    <t>【追蹤者】發動絕招時，能燃起火焰、蔓延周圍</t>
-  </si>
-  <si>
     <t>【女爵】以短劍使出連續攻擊時，
 能對著周圍的敵人，再次上演最近做過的行動</t>
   </si>
@@ -318,43 +294,18 @@
     <t>【無賴】提升技藝傷害，但降低技藝發動期間的減傷率</t>
   </si>
   <si>
-    <t>【復仇者】發動絕招時，能以自己的血量為代價
-完全恢復周圍我方人物的血量</t>
-  </si>
-  <si>
     <t>【守護者】延長技藝的有效時間</t>
   </si>
   <si>
-    <t>【守護者】發動絕招時，能提升周圍我方人物的減傷率</t>
-  </si>
-  <si>
-    <t>【復仇者】發動絕招時，能引發靈火爆炸</t>
-  </si>
-  <si>
-    <t>【守護者】發動技藝時，能恢復周圍我方人物的血量</t>
-  </si>
-  <si>
     <t>【追蹤者】技藝會附加引發異常狀態出血的效果</t>
   </si>
   <si>
     <t>【守護者】以戟蓄力攻擊時，能引發旋風</t>
   </si>
   <si>
-    <t>【執行者】在絕招發動期間，能以咆哮恢復血量</t>
-  </si>
-  <si>
     <t>【守護者】技藝會附加聖屬性攻擊力</t>
   </si>
   <si>
-    <t>【守護者】發動絕招時，能緩慢恢復周圍我方人物的血量</t>
-  </si>
-  <si>
-    <t>血量偏低時，包含周圍我方人物緩慢恢復血量</t>
-  </si>
-  <si>
-    <t>血量偏低時，能提升減傷率</t>
-  </si>
-  <si>
     <t>重攻擊時，能朝周圍引發熱浪</t>
   </si>
   <si>
@@ -373,26 +324,10 @@
     <t>身在圖騰碑石周圍時，能提升強韌度</t>
   </si>
   <si>
-    <t>食用苔藥等等道具時，能恢復血量</t>
-  </si>
-  <si>
-    <t>【追蹤者】發動絕招後，
-能提升攻擊力與精力上限，但降低減傷率</t>
-  </si>
-  <si>
-    <t>防禦成功時，能累積絕招量表</t>
-  </si>
-  <si>
     <t>防禦時，變得容易被敵人攻擊</t>
   </si>
   <si>
-    <t>使出致命一擊時，加快累積絕招量表</t>
-  </si>
-  <si>
     <t>塗抹油脂類道具時，能額外提升攻擊力</t>
-  </si>
-  <si>
-    <t>【復仇者】發動絕招時，能強化家人與我方人物</t>
   </si>
   <si>
     <t>【無賴】在技藝發動期間，受到攻擊時
@@ -421,19 +356,9 @@
     <t>【追蹤者】發動技藝時，能提升攻擊力</t>
   </si>
   <si>
-    <t>【追蹤者】發動能力時，能累積絕招量表</t>
-  </si>
-  <si>
-    <t>【女爵】在絕招發動期間，打倒敵人時能提升攻擊力</t>
-  </si>
-  <si>
     <t>【隱士】收集屬性痕時，能觸發“魔法之境”</t>
   </si>
   <si>
-    <t>【隱士】發動絕招時，
-自己陷入異常狀態出血，提升攻擊力</t>
-  </si>
-  <si>
     <t>【追蹤者】發動能力時，能提升攻擊力</t>
   </si>
   <si>
@@ -446,9 +371,6 @@
     <t>【守護者】在能力發動期間，防禦成功時能形成衝擊波</t>
   </si>
   <si>
-    <t>【女爵】延長絕招的有效時間</t>
-  </si>
-  <si>
     <t>以特大武器蓄力攻擊時，岩石會攀附在武器上</t>
   </si>
   <si>
@@ -459,12 +381,6 @@
   </si>
   <si>
     <t>【隱士】收集四種屬性痕時，能提升屬性攻擊力</t>
-  </si>
-  <si>
-    <t>【隱士】發動絕招時，能提升血量上限</t>
-  </si>
-  <si>
-    <t>【執行者】在絕招發動期間，能提升攻擊力</t>
   </si>
   <si>
     <t>【執行者】強化能力的效果，但降低對異常狀態的抵抗力</t>
@@ -474,22 +390,9 @@
 但攻擊時會降低減傷率</t>
   </si>
   <si>
-    <t>【執行者】在技藝發動期間，
-妖刀進入解放狀態時，能恢復血量</t>
-  </si>
-  <si>
-    <t>【鐵之眼】蓄力發動絕招時，附加異常狀態中毒</t>
-  </si>
-  <si>
-    <t>【鐵之眼】發動絕招後，強化突刺反擊</t>
-  </si>
-  <si>
     <t>使出火屬性的致命一擊時，能提升精力上限</t>
   </si>
   <si>
-    <t>使出致命一擊時，能恢復血量</t>
-  </si>
-  <si>
     <t>使出致命一擊時，能附加雷屬性攻擊力</t>
   </si>
   <si>
@@ -502,12 +405,6 @@
     <t>使出致命一擊時，能形成催眠煙霧</t>
   </si>
   <si>
-    <t>通過肢體動作“盤腿坐”，能累積發狂量表</t>
-  </si>
-  <si>
-    <t>引發異常狀態發狂後，能持續恢復專注值</t>
-  </si>
-  <si>
     <t>急速衝刺期間落地時，能造成地面裂開</t>
   </si>
   <si>
@@ -520,12 +417,6 @@
     <t>切換武器時，能提升物理攻擊力</t>
   </si>
   <si>
-    <t>連續攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>防禦成功時，恢復血量</t>
-  </si>
-  <si>
     <t>強化輕攻擊的第一記攻擊</t>
   </si>
   <si>
@@ -607,9 +498,6 @@
     <t>每次打倒封印監牢裡的囚犯，能永久性提升攻擊力</t>
   </si>
   <si>
-    <t>每次解開魔法師塔的機關，能永久性提升專注值上限</t>
-  </si>
-  <si>
     <t>每次打倒黑夜入侵者，能提升攻擊力</t>
   </si>
   <si>
@@ -683,30 +571,6 @@
   </si>
   <si>
     <t>裝備三把以上類別為弓的武器，能提升攻擊力</t>
-  </si>
-  <si>
-    <t>裝備三把以上類別為手杖的武器，能提升專注值上限</t>
-  </si>
-  <si>
-    <t>裝備三把以上類別為聖印記的武器，能提升專注值上限</t>
-  </si>
-  <si>
-    <t>裝備三把以上類別為小盾的武器，能提升血量上限</t>
-  </si>
-  <si>
-    <t>裝備三把以上類別為中盾的武器，能提升血量上限</t>
-  </si>
-  <si>
-    <t>裝備三把以上類別為大盾的武器，能提升血量上限</t>
-  </si>
-  <si>
-    <t>提升打倒敵人時，絕招量表的累積量表</t>
-  </si>
-  <si>
-    <t>打倒敵人時，除了自己恢復周圍我方人物的血量</t>
-  </si>
-  <si>
-    <t>在圖騰碑石周圍打倒敵人時，能恢復血量</t>
   </si>
   <si>
     <t>對陷入中毒的敵人
@@ -866,15 +730,6 @@
     <t>出擊時，會持有“星光碎片”</t>
   </si>
   <si>
-    <t>防禦反擊成功時，能依照自己目前的血量提升傷害</t>
-  </si>
-  <si>
-    <t>突刺反擊成功時，能恢復血量</t>
-  </si>
-  <si>
-    <t>頭部射擊時，能恢復血量</t>
-  </si>
-  <si>
     <t>頭部射擊時，能提升讓敵人失去平衡的能力</t>
   </si>
   <si>
@@ -902,9 +757,6 @@
     <t>對陷入凍傷的敵人，能強化攻擊</t>
   </si>
   <si>
-    <t>對陷入催眠的敵人，能通過攻擊引發魔力爆炸</t>
-  </si>
-  <si>
     <t>周圍人物陷入異常狀態凍傷時，能隱藏自己的身影</t>
   </si>
   <si>
@@ -923,9 +775,6 @@
     <t>【女爵】發動技藝時，能催眠敵人</t>
   </si>
   <si>
-    <t>【無賴】延長絕招的有效時間</t>
-  </si>
-  <si>
     <t>【復仇者】提升能力的發動機率</t>
   </si>
   <si>
@@ -999,150 +848,6 @@
   </si>
   <si>
     <t>提升弓的攻擊力</t>
-  </si>
-  <si>
-    <t>以短劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以直劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以大劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以特大劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以曲劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以刀攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以雙頭劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以刺劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以重刺劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以斧攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以大斧攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以槌攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以大槌攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以連枷攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以矛攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以長矛攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以大矛攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以戟攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以鐮刀攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以拳頭攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以鉤爪攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以軟鞭攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以特大武器攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以弓攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以短劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以直劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以大劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以特大劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以曲劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以刀攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以雙頭劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以刺劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以重刺劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以斧攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以大斧攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以槌攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以大槌攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以連枷攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以矛攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以長矛攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以大矛攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以戟攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以鐮刀攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以拳頭攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以鉤爪攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以軟鞭攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以特大武器攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>以弓攻擊時，恢復專注值</t>
   </si>
   <si>
     <t>夜與火的庇佑</t>
@@ -1251,108 +956,9 @@
     <t>執行者的不甘</t>
   </si>
   <si>
-    <t>通過潛在能力，能比較容易找到短劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到直劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到特大劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到曲劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到刀</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到雙頭劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到刺劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到重刺劍</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到斧</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大斧</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到槌</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大槌</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到連枷</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到矛</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大矛</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到戟</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到鐮刀</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到拳頭</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到鉤爪</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到軟鞭</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到特大武器</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到弓</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大弓</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到弩</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到弩炮</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到小盾</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到中盾</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大盾</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到手杖</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到聖印記</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到火把</t>
-  </si>
-  <si>
     <t>延長魔法、禱告的有效時間</t>
   </si>
   <si>
-    <t>持續恢復專注值</t>
-  </si>
-  <si>
     <t>提升近戰攻擊力</t>
   </si>
   <si>
@@ -1365,13 +971,7 @@
     <t>【學者】使用技藝時，提升目標我方人物的攻擊力</t>
   </si>
   <si>
-    <t>【學者】對上已用絕招連結的敵人，持續給予傷害</t>
-  </si>
-  <si>
     <t>【學者】每次使用技藝增加樣本，能獲得盧恩</t>
-  </si>
-  <si>
-    <t>【送葬者】發動絕招時，提升攻擊力</t>
   </si>
   <si>
     <t>【送葬者】連擊的最後攻擊命中時，提升攻擊力</t>
@@ -1381,9 +981,6 @@
 提升物理攻擊力</t>
   </si>
   <si>
-    <t>【送葬者】發動絕招時，恢復觸碰到的我方人物的血量</t>
-  </si>
-  <si>
     <t>連續攻擊時，提升攻擊力</t>
   </si>
   <si>
@@ -1396,9 +993,6 @@
     <t>受到損傷時，附加異常狀態腐敗</t>
   </si>
   <si>
-    <t>周圍陷入腐敗時，持續恢復血量</t>
-  </si>
-  <si>
     <t>出擊時，武器魔法改為“魔法輝劍</t>
   </si>
   <si>
@@ -1462,12 +1056,6 @@
     <t>縮短技藝的冷卻時間＋５</t>
   </si>
   <si>
-    <t>加快累積絕招量表＋４</t>
-  </si>
-  <si>
-    <t>加快累積絕招量表＋５</t>
-  </si>
-  <si>
     <t>強韌度＋４</t>
   </si>
   <si>
@@ -1570,12 +1158,6 @@
     <t>提升對發狂的抵抗力＋２</t>
   </si>
   <si>
-    <t>受到損傷的當下，能通過攻擊恢復部分血量＋１</t>
-  </si>
-  <si>
-    <t>受到損傷的當下，能通過攻擊恢復部分血量＋２</t>
-  </si>
-  <si>
     <t>提升雙手共持時，造成失去平衡的能力＋１</t>
   </si>
   <si>
@@ -1588,30 +1170,6 @@
     <t>提升雙手各持時，造成失去平衡的能力＋２</t>
   </si>
   <si>
-    <t>血量偏低時，提升減傷率＋１</t>
-  </si>
-  <si>
-    <t>血量偏低時，提升減傷率＋２</t>
-  </si>
-  <si>
-    <t>食用苔藥等等道具時，能恢復血量＋１</t>
-  </si>
-  <si>
-    <t>食用苔藥等等道具時，能恢復血量＋２</t>
-  </si>
-  <si>
-    <t>防禦成功時，能累積絕招量表＋１</t>
-  </si>
-  <si>
-    <t>防禦成功時，能累積絕招量表＋２</t>
-  </si>
-  <si>
-    <t>使出致命一擊時，加快累積絕招量表＋１</t>
-  </si>
-  <si>
-    <t>使出致命一擊時，加快累積絕招量表＋２</t>
-  </si>
-  <si>
     <t>塗抹油脂類道具時，能額外提升物理攻擊力＋１</t>
   </si>
   <si>
@@ -1678,9 +1236,6 @@
     <t>強化調香術＋２</t>
   </si>
   <si>
-    <t>每次打倒大教堂的強敵，能提升血量上限</t>
-  </si>
-  <si>
     <t>每次打倒小型要塞的強敵，能增加獲得的盧恩、提升觀察力</t>
   </si>
   <si>
@@ -1688,18 +1243,6 @@
   </si>
   <si>
     <t>每次打倒大型營地的強敵，能提升精力上限</t>
-  </si>
-  <si>
-    <t>提升打倒敵人時，絕招量表的累積量＋１</t>
-  </si>
-  <si>
-    <t>提升打倒敵人時，絕招量表的累積量＋２</t>
-  </si>
-  <si>
-    <t>突刺反擊成功時，能恢復血量＋１</t>
-  </si>
-  <si>
-    <t>突刺反擊成功時，能恢復血量＋２</t>
   </si>
   <si>
     <t>對陷入中毒的敵人，能強化攻擊＋１</t>
@@ -1733,15 +1276,9 @@
     <t>【無賴】技藝命中敵人時，能降低對方的攻擊力</t>
   </si>
   <si>
-    <t>【復仇者】發動能力時，能提升專注值上限</t>
-  </si>
-  <si>
     <t>【隱士】收集屬性痕時，能提升該屬性的減傷率</t>
   </si>
   <si>
-    <t>【執行者】發動能力時，能緩慢恢復血量</t>
-  </si>
-  <si>
     <t>周圍陷入催眠時，提升攻擊力</t>
   </si>
   <si>
@@ -1758,15 +1295,6 @@
   </si>
   <si>
     <t>周圍陷入發狂時，提升攻擊力＋２</t>
-  </si>
-  <si>
-    <t>減少專注值消耗</t>
-  </si>
-  <si>
-    <t>減少專注值消耗＋１</t>
-  </si>
-  <si>
-    <t>減少專注值消耗＋２</t>
   </si>
   <si>
     <t>提升屬性攻擊力</t>
@@ -2004,9 +1532,6 @@
     <t>降低聖盃瓶恢復量</t>
   </si>
   <si>
-    <t>降低絕招量表累積量</t>
-  </si>
-  <si>
     <t>降低物理減傷率</t>
   </si>
   <si>
@@ -2019,9 +1544,6 @@
     <t>增加急速衝刺的精力消耗</t>
   </si>
   <si>
-    <t>持續減少血量</t>
-  </si>
-  <si>
     <t>增加閃避時的精力消耗</t>
   </si>
   <si>
@@ -2040,28 +1562,7 @@
     <t>使用聖盃瓶時，累積發狂量表</t>
   </si>
   <si>
-    <t>血量沒有全滿時，降低攻擊力</t>
-  </si>
-  <si>
-    <t>血量沒有全滿時，累積中毒量表</t>
-  </si>
-  <si>
-    <t>血量沒有全滿時，累積猩紅腐敗量表</t>
-  </si>
-  <si>
-    <t>血量全滿時，降低攻擊力</t>
-  </si>
-  <si>
     <t>瀕死時，翻倒聖盃瓶</t>
-  </si>
-  <si>
-    <t>瀕死時，降低血量上限</t>
-  </si>
-  <si>
-    <t>【學者】對自己使用技藝時，能減少消耗的專注值</t>
-  </si>
-  <si>
-    <t>【送葬者】發動絕招後，能再次使用技藝</t>
   </si>
   <si>
     <t>【學者】提升集中力，但降低生命力</t>
@@ -2091,13 +1592,519 @@
     <t>提升大曲劍的攻擊力</t>
   </si>
   <si>
-    <t>以大曲劍攻擊時，恢復血量</t>
-  </si>
-  <si>
-    <t>以大曲劍攻擊時，恢復專注值</t>
-  </si>
-  <si>
-    <t>通過潛在能力，能比較容易找到大曲劍</t>
+    <t>使出致命一擊時，能累積絕活量表＋１</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使出致命一擊時，能累積絕活量表＋２</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打倒敵人時，能累積絕活量表＋１</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打倒敵人時，能累積絕活量表＋２</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然累積絕活量表＋１</t>
+  </si>
+  <si>
+    <t>自然累積絕活量表＋２</t>
+  </si>
+  <si>
+    <t>【追蹤者】發動絕活時，能燃起火焰、蔓延周圍</t>
+  </si>
+  <si>
+    <t>【守護者】發動絕活時，能提升周圍我方人物的減傷率</t>
+  </si>
+  <si>
+    <t>【復仇者】發動絕活時，能引發靈火爆炸</t>
+  </si>
+  <si>
+    <t>【追蹤者】發動絕活後，
+能提升攻擊力與精力上限，但降低減傷率</t>
+  </si>
+  <si>
+    <t>防禦成功時，能累積絕活量表</t>
+  </si>
+  <si>
+    <t>使出致命一擊時，能累積絕活量表</t>
+  </si>
+  <si>
+    <t>【復仇者】發動絕活時，能強化家人與我方人物</t>
+  </si>
+  <si>
+    <t>【追蹤者】發動能力時，能累積絕活量表</t>
+  </si>
+  <si>
+    <t>【女爵】在絕活發動期間，打倒敵人時能提升攻擊力</t>
+  </si>
+  <si>
+    <t>【隱士】發動絕活時，
+自己陷入異常狀態出血，提升攻擊力</t>
+  </si>
+  <si>
+    <t>【女爵】延長絕活的有效時間</t>
+  </si>
+  <si>
+    <t>【執行者】在絕活發動期間，能提升攻擊力</t>
+  </si>
+  <si>
+    <t>【鐵之眼】蓄力發動絕活時，附加異常狀態中毒</t>
+  </si>
+  <si>
+    <t>【鐵之眼】發動絕活後，強化突刺反擊</t>
+  </si>
+  <si>
+    <t>打倒敵人時，能累積絕活量表</t>
+  </si>
+  <si>
+    <t>【無賴】延長絕活的有效時間</t>
+  </si>
+  <si>
+    <t>【學者】對上已用絕活連結的敵人，持續給予傷害</t>
+  </si>
+  <si>
+    <t>【送葬者】發動絕活時，提升攻擊力</t>
+  </si>
+  <si>
+    <t>自然累積絕活量表＋３</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然累積絕活量表＋４</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然累積絕活量表＋５</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防禦成功時，能累積絕活量表＋１</t>
+  </si>
+  <si>
+    <t>防禦成功時，能累積絕活量表＋２</t>
+  </si>
+  <si>
+    <t>降低絕活量表累積</t>
+  </si>
+  <si>
+    <t>【送葬者】發動絕活後，能再次使用技藝</t>
+  </si>
+  <si>
+    <t>提升HP上限</t>
+  </si>
+  <si>
+    <t>持續恢復HP</t>
+  </si>
+  <si>
+    <t>受到損傷的當下，能透過攻擊恢復部分HP</t>
+  </si>
+  <si>
+    <t>【復仇者】發動絕活時，能以自己的HP為代價
+完全恢復周圍我方人物的HP</t>
+  </si>
+  <si>
+    <t>【守護者】發動技藝時，能恢復周圍我方人物的HP</t>
+  </si>
+  <si>
+    <t>【執行者】在絕活發動期間，能以咆哮恢復HP</t>
+  </si>
+  <si>
+    <t>【守護者】發動絕活時，能緩慢恢復周圍我方人物的HP</t>
+  </si>
+  <si>
+    <t>HP偏低時，包含周圍我方人物緩慢恢復HP</t>
+  </si>
+  <si>
+    <t>HP偏低時，能提升減傷率</t>
+  </si>
+  <si>
+    <t>食用苔藥等等道具時，能恢復HP</t>
+  </si>
+  <si>
+    <t>【隱士】發動絕活時，能提升HP上限</t>
+  </si>
+  <si>
+    <t>【執行者】在技藝發動期間，
+妖刀進入解放狀態時，能恢復HP</t>
+  </si>
+  <si>
+    <t>使出致命一擊時，能恢復HP</t>
+  </si>
+  <si>
+    <t>防禦成功時，恢復HP</t>
+  </si>
+  <si>
+    <t>裝備三把以上類別為小盾的武器，能提升HP上限</t>
+  </si>
+  <si>
+    <t>裝備三把以上類別為中盾的武器，能提升HP上限</t>
+  </si>
+  <si>
+    <t>裝備三把以上類別為大盾的武器，能提升HP上限</t>
+  </si>
+  <si>
+    <t>打倒敵人時，除了自己恢復周圍我方人物的HP</t>
+  </si>
+  <si>
+    <t>在圖騰碑石周圍打倒敵人時，能恢復HP</t>
+  </si>
+  <si>
+    <t>防禦反擊成功時，能依照自己目前的HP提升傷害</t>
+  </si>
+  <si>
+    <t>突刺反擊成功時，能恢復HP</t>
+  </si>
+  <si>
+    <t>頭部射擊時，能恢復HP</t>
+  </si>
+  <si>
+    <t>以短劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以直劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以大劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以特大劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以曲劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以大曲劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以刀攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以雙頭劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以刺劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以重刺劍攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以斧攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以大斧攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以槌攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以大槌攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以連枷攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以矛攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以長矛攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以大矛攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以戟攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以鐮刀攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以拳頭攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以鉤爪攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以軟鞭攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以特大武器攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>以弓攻擊時，恢復HP</t>
+  </si>
+  <si>
+    <t>【送葬者】發動絕活時，恢復觸碰到的我方人物的HP</t>
+  </si>
+  <si>
+    <t>周圍陷入腐敗時，持續恢復HP</t>
+  </si>
+  <si>
+    <t>HP偏低時，提升減傷率＋１</t>
+  </si>
+  <si>
+    <t>HP偏低時，提升減傷率＋２</t>
+  </si>
+  <si>
+    <t>食用苔藥等等道具時，能恢復HP＋１</t>
+  </si>
+  <si>
+    <t>食用苔藥等等道具時，能恢復HP＋２</t>
+  </si>
+  <si>
+    <t>每次打倒大教堂的強敵，能提升HP上限</t>
+  </si>
+  <si>
+    <t>突刺反擊成功時，能恢復HP＋１</t>
+  </si>
+  <si>
+    <t>突刺反擊成功時，能恢復HP＋２</t>
+  </si>
+  <si>
+    <t>【執行者】發動能力時，能緩慢恢復HP</t>
+  </si>
+  <si>
+    <t>持續減少HP</t>
+  </si>
+  <si>
+    <t>HP沒有全滿時，降低攻擊力</t>
+  </si>
+  <si>
+    <t>HP沒有全滿時，累積中毒量表</t>
+  </si>
+  <si>
+    <t>HP沒有全滿時，累積猩紅腐敗量表</t>
+  </si>
+  <si>
+    <t>HP全滿時，降低攻擊力</t>
+  </si>
+  <si>
+    <t>瀕死時，降低HP上限</t>
+  </si>
+  <si>
+    <t>透過肢體動作“盤腿坐”，能累積發狂量表</t>
+  </si>
+  <si>
+    <t>對陷入催眠的敵人，能透過攻擊引發魔力爆炸</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到短劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到直劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到特大劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到曲劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大曲劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到刀</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到雙頭劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到刺劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到重刺劍</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到斧</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大斧</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到槌</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大槌</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到連枷</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到矛</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大矛</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到戟</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到鐮刀</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到拳頭</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到鉤爪</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到軟鞭</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到特大武器</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到弓</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大弓</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到弩</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到弩炮</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到小盾</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到中盾</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到大盾</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到手杖</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到聖印記</t>
+  </si>
+  <si>
+    <t>透過潛在能力，能比較容易找到火把</t>
+  </si>
+  <si>
+    <t>受到損傷的當下，能透過攻擊恢復部分HP＋１</t>
+  </si>
+  <si>
+    <t>受到損傷的當下，能透過攻擊恢復部分HP＋２</t>
+  </si>
+  <si>
+    <t>【學者】對自己使用技藝時，能減少消耗的FP</t>
+  </si>
+  <si>
+    <t>提升FP上限</t>
+  </si>
+  <si>
+    <t>引發異常狀態發狂後，能持續恢復FP</t>
+  </si>
+  <si>
+    <t>連續攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>每次解開魔法師塔的機關，能提升FP上限</t>
+  </si>
+  <si>
+    <t>裝備三把以上類別為手杖的武器，能提升FP上限</t>
+  </si>
+  <si>
+    <t>裝備三把以上類別為聖印記的武器，能提升FP上限</t>
+  </si>
+  <si>
+    <t>以短劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以直劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以大劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以特大劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以曲劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以大曲劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以刀攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以雙頭劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以刺劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以重刺劍攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以斧攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以大斧攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以槌攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以大槌攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以連枷攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以矛攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以長矛攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以大矛攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以戟攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以鐮刀攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以拳頭攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以鉤爪攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以軟鞭攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以特大武器攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>以弓攻擊時，恢復FP</t>
+  </si>
+  <si>
+    <t>持續恢復FP</t>
+  </si>
+  <si>
+    <t>【復仇者】發動能力時，能提升FP上限</t>
+  </si>
+  <si>
+    <t>減少FP消耗</t>
+  </si>
+  <si>
+    <t>減少FP消耗＋１</t>
+  </si>
+  <si>
+    <t>減少FP消耗＋２</t>
   </si>
 </sst>
 </file>
@@ -2470,17 +2477,17 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>550</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2492,7 +2499,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2504,7 +2511,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -2516,17 +2523,17 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>651</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2538,7 +2545,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2550,7 +2557,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2562,17 +2569,17 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2584,7 +2591,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -2596,7 +2603,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -2608,7 +2615,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -2620,7 +2627,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -2632,7 +2639,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
@@ -2644,7 +2651,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>5</v>
@@ -2656,7 +2663,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>5</v>
@@ -2668,7 +2675,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>5</v>
@@ -2680,7 +2687,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>5</v>
@@ -2692,7 +2699,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>5</v>
@@ -2704,7 +2711,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>5</v>
@@ -2716,7 +2723,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>5</v>
@@ -2728,7 +2735,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>5</v>
@@ -2740,7 +2747,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>5</v>
@@ -2752,7 +2759,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
@@ -2764,7 +2771,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>5</v>
@@ -2776,7 +2783,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
@@ -2788,7 +2795,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>523</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>5</v>
@@ -2800,7 +2807,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>524</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>5</v>
@@ -2810,9 +2817,9 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>38</v>
+    <row r="34" spans="1:4" ht="15">
+      <c r="A34" s="3" t="s">
+        <v>543</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
@@ -2824,7 +2831,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>5</v>
@@ -2836,7 +2843,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>5</v>
@@ -2848,7 +2855,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>5</v>
@@ -2860,7 +2867,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>551</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>5</v>
@@ -2870,7 +2877,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>5</v>
@@ -2882,7 +2889,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
@@ -2894,7 +2901,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>5</v>
@@ -2908,7 +2915,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>5</v>
@@ -2920,7 +2927,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>5</v>
@@ -2932,7 +2939,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
@@ -2946,7 +2953,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>5</v>
@@ -2958,7 +2965,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>5</v>
@@ -2970,7 +2977,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>5</v>
@@ -2984,7 +2991,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>5</v>
@@ -2996,7 +3003,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>5</v>
@@ -3008,7 +3015,7 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
@@ -3022,7 +3029,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
@@ -3034,7 +3041,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
@@ -3046,7 +3053,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>5</v>
@@ -3060,10 +3067,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C54" s="2">
         <v>2</v>
@@ -3074,7 +3081,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3082,7 +3089,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3090,10 +3097,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
@@ -3102,7 +3109,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3110,7 +3117,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3118,10 +3125,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
@@ -3130,7 +3137,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3138,7 +3145,7 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3146,7 +3153,7 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3154,7 +3161,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3162,10 +3169,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2">
@@ -3174,7 +3181,7 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3182,7 +3189,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3190,10 +3197,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
@@ -3202,7 +3209,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3210,7 +3217,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3218,7 +3225,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3226,7 +3233,7 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3234,7 +3241,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>5</v>
@@ -3244,7 +3251,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>5</v>
@@ -3254,7 +3261,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>5</v>
@@ -3264,7 +3271,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>5</v>
@@ -3274,7 +3281,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
@@ -3284,7 +3291,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>5</v>
@@ -3294,7 +3301,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
@@ -3304,7 +3311,7 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>5</v>
@@ -3314,7 +3321,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>5</v>
@@ -3324,7 +3331,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>5</v>
@@ -3334,7 +3341,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>5</v>
@@ -3343,11 +3350,11 @@
       <c r="D83" s="2"/>
     </row>
     <row r="84" spans="1:4" ht="28.5">
-      <c r="A84" s="2" t="s">
-        <v>88</v>
+      <c r="A84" s="3" t="s">
+        <v>552</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2">
@@ -3356,7 +3363,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>5</v>
@@ -3368,7 +3375,7 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>5</v>
@@ -3380,7 +3387,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>5</v>
@@ -3390,7 +3397,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3398,10 +3405,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2">
@@ -3410,10 +3417,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2" t="s">
-        <v>95</v>
+        <v>525</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C90" s="2">
         <v>2</v>
@@ -3424,10 +3431,10 @@
     </row>
     <row r="91" spans="1:4" ht="28.5">
       <c r="A91" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C91" s="2">
         <v>2</v>
@@ -3438,18 +3445,18 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="1:4" ht="28.5">
-      <c r="A93" s="2" t="s">
-        <v>98</v>
+    <row r="93" spans="1:4" ht="30">
+      <c r="A93" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2">
@@ -3458,10 +3465,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2">
@@ -3470,7 +3477,7 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>100</v>
+        <v>526</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -3478,10 +3485,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2" t="s">
-        <v>101</v>
+        <v>527</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C96" s="2">
         <v>2</v>
@@ -3492,7 +3499,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2" t="s">
-        <v>102</v>
+        <v>554</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3500,7 +3507,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="2">
@@ -3512,10 +3519,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2">
@@ -3524,10 +3531,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2" t="s">
-        <v>105</v>
+        <v>555</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2">
@@ -3536,7 +3543,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -3544,10 +3551,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2" t="s">
-        <v>107</v>
+        <v>556</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2">
@@ -3556,10 +3563,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2" t="s">
-        <v>108</v>
+        <v>557</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2">
@@ -3568,7 +3575,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2" t="s">
-        <v>109</v>
+        <v>558</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>5</v>
@@ -3580,7 +3587,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -3588,7 +3595,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -3596,7 +3603,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -3604,7 +3611,7 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -3612,10 +3619,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2">
@@ -3624,27 +3631,27 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
     </row>
     <row r="111" spans="1:4" ht="28.5">
       <c r="A111" s="2" t="s">
-        <v>116</v>
+        <v>559</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
     </row>
     <row r="112" spans="1:4" ht="28.5">
       <c r="A112" s="2" t="s">
-        <v>117</v>
+        <v>528</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -3652,10 +3659,10 @@
     </row>
     <row r="113" spans="1:4" ht="28.5">
       <c r="A113" s="2" t="s">
-        <v>118</v>
+        <v>529</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C113" s="2">
         <v>3</v>
@@ -3666,10 +3673,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C114" s="2">
         <v>2</v>
@@ -3679,11 +3686,11 @@
       </c>
     </row>
     <row r="115" spans="1:4" ht="28.5">
-      <c r="A115" s="2" t="s">
-        <v>120</v>
+      <c r="A115" s="3" t="s">
+        <v>530</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C115" s="2">
         <v>3</v>
@@ -3694,10 +3701,10 @@
     </row>
     <row r="116" spans="1:4" ht="28.5">
       <c r="A116" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2">
@@ -3706,10 +3713,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2">
@@ -3718,10 +3725,10 @@
     </row>
     <row r="118" spans="1:4" ht="28.5">
       <c r="A118" s="2" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C118" s="2">
         <v>2</v>
@@ -3732,7 +3739,7 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -3740,7 +3747,7 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -3748,7 +3755,7 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -3756,10 +3763,10 @@
     </row>
     <row r="122" spans="1:4" ht="28.5">
       <c r="A122" s="2" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2">
@@ -3768,10 +3775,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2">
@@ -3780,10 +3787,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2">
@@ -3792,7 +3799,7 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -3800,10 +3807,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2" t="s">
-        <v>131</v>
+        <v>532</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2">
@@ -3812,10 +3819,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2" t="s">
-        <v>132</v>
+        <v>533</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2">
@@ -3824,10 +3831,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C128" s="2">
         <v>2</v>
@@ -3838,10 +3845,10 @@
     </row>
     <row r="129" spans="1:4" ht="28.5">
       <c r="A129" s="2" t="s">
-        <v>134</v>
+        <v>534</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C129" s="2">
         <v>2</v>
@@ -3852,7 +3859,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -3860,10 +3867,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C131" s="2">
         <v>2</v>
@@ -3874,20 +3881,20 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C133" s="2">
         <v>2</v>
@@ -3898,7 +3905,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2" t="s">
-        <v>139</v>
+        <v>535</v>
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -3906,7 +3913,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -3914,7 +3921,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -3922,7 +3929,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -3930,7 +3937,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -3938,10 +3945,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2" t="s">
-        <v>144</v>
+        <v>560</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2">
@@ -3950,7 +3957,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2" t="s">
-        <v>145</v>
+        <v>536</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -3958,7 +3965,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -3966,10 +3973,10 @@
     </row>
     <row r="142" spans="1:4" ht="28.5">
       <c r="A142" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2">
@@ -3978,10 +3985,10 @@
     </row>
     <row r="143" spans="1:4" ht="28.5">
       <c r="A143" s="2" t="s">
-        <v>148</v>
+        <v>561</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2">
@@ -3990,10 +3997,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2" t="s">
-        <v>149</v>
+        <v>537</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C144" s="2">
         <v>2</v>
@@ -4004,10 +4011,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2" t="s">
-        <v>150</v>
+        <v>538</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2">
@@ -4016,7 +4023,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -4024,7 +4031,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2" t="s">
-        <v>152</v>
+        <v>562</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -4032,7 +4039,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -4040,10 +4047,10 @@
     </row>
     <row r="149" spans="1:4" ht="28.5">
       <c r="A149" s="2" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2">
@@ -4052,7 +4059,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -4060,7 +4067,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -4068,17 +4075,17 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2" t="s">
-        <v>157</v>
+        <v>613</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2" t="s">
-        <v>158</v>
+        <v>652</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>5</v>
@@ -4088,7 +4095,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -4096,17 +4103,17 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>5</v>
@@ -4116,17 +4123,17 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2" t="s">
-        <v>163</v>
+        <v>653</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>5</v>
@@ -4136,10 +4143,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2" t="s">
-        <v>164</v>
+        <v>563</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2">
@@ -4148,7 +4155,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>5</v>
@@ -4162,7 +4169,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>5</v>
@@ -4174,7 +4181,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>5</v>
@@ -4186,10 +4193,10 @@
     </row>
     <row r="163" spans="1:4" ht="28.5">
       <c r="A163" s="2" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2">
@@ -4198,7 +4205,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -4206,10 +4213,10 @@
     </row>
     <row r="165" spans="1:4" ht="15">
       <c r="A165" s="3" t="s">
-        <v>680</v>
+        <v>515</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>681</v>
+        <v>516</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2">
@@ -4218,7 +4225,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>5</v>
@@ -4230,7 +4237,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>5</v>
@@ -4242,7 +4249,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>5</v>
@@ -4254,7 +4261,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>5</v>
@@ -4266,7 +4273,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>5</v>
@@ -4278,7 +4285,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>5</v>
@@ -4292,7 +4299,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>5</v>
@@ -4306,7 +4313,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>5</v>
@@ -4316,7 +4323,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>5</v>
@@ -4330,7 +4337,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>5</v>
@@ -4344,7 +4351,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>5</v>
@@ -4354,7 +4361,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -4362,7 +4369,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>5</v>
@@ -4376,7 +4383,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>5</v>
@@ -4390,7 +4397,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>5</v>
@@ -4404,7 +4411,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>5</v>
@@ -4418,7 +4425,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>5</v>
@@ -4432,7 +4439,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>5</v>
@@ -4446,7 +4453,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>5</v>
@@ -4460,10 +4467,10 @@
     </row>
     <row r="185" spans="1:4" ht="28.5">
       <c r="A185" s="2" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2">
@@ -4472,10 +4479,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2">
@@ -4484,10 +4491,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C187" s="2">
         <v>2</v>
@@ -4496,12 +4503,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
-      <c r="A188" s="2" t="s">
-        <v>192</v>
+    <row r="188" spans="1:4" ht="15">
+      <c r="A188" s="3" t="s">
+        <v>654</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C188" s="2">
         <v>2</v>
@@ -4512,10 +4519,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C189" s="2">
         <v>2</v>
@@ -4526,10 +4533,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2">
@@ -4538,10 +4545,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
@@ -4552,10 +4559,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C192" s="2">
         <v>1</v>
@@ -4566,10 +4573,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C193" s="2">
         <v>1</v>
@@ -4580,10 +4587,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="2" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C194" s="2">
         <v>1</v>
@@ -4594,10 +4601,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="2" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C195" s="2">
         <v>1</v>
@@ -4608,10 +4615,10 @@
     </row>
     <row r="196" spans="1:4" ht="15">
       <c r="A196" s="3" t="s">
-        <v>682</v>
+        <v>517</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C196" s="2">
         <v>1</v>
@@ -4622,10 +4629,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="2" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
@@ -4636,10 +4643,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="2" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C198" s="2">
         <v>1</v>
@@ -4650,10 +4657,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="2" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C199" s="2">
         <v>1</v>
@@ -4664,10 +4671,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="2" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C200" s="2">
         <v>1</v>
@@ -4678,10 +4685,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="2" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C201" s="2">
         <v>1</v>
@@ -4692,10 +4699,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="2" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C202" s="2">
         <v>1</v>
@@ -4706,10 +4713,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="2" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C203" s="2">
         <v>1</v>
@@ -4720,10 +4727,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="2" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C204" s="2">
         <v>1</v>
@@ -4734,10 +4741,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="2" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
@@ -4748,10 +4755,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="2" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C206" s="2">
         <v>1</v>
@@ -4762,10 +4769,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="2" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
@@ -4776,10 +4783,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="2" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C208" s="2">
         <v>1</v>
@@ -4790,10 +4797,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="2" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C209" s="2">
         <v>1</v>
@@ -4804,10 +4811,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="2" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
@@ -4818,10 +4825,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="2" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
@@ -4832,10 +4839,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="2" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -4846,10 +4853,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="2" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
@@ -4860,10 +4867,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="2" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
@@ -4874,10 +4881,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="2" t="s">
-        <v>218</v>
+        <v>655</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C215" s="2">
         <v>1</v>
@@ -4888,10 +4895,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="2" t="s">
-        <v>219</v>
+        <v>656</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
@@ -4902,10 +4909,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="2" t="s">
-        <v>220</v>
+        <v>564</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C217" s="2">
         <v>1</v>
@@ -4916,10 +4923,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="2" t="s">
-        <v>221</v>
+        <v>565</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C218" s="2">
         <v>1</v>
@@ -4930,10 +4937,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="2" t="s">
-        <v>222</v>
+        <v>566</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
@@ -4943,11 +4950,11 @@
       </c>
     </row>
     <row r="220" spans="1:4" ht="28.5">
-      <c r="A220" s="2" t="s">
-        <v>223</v>
+      <c r="A220" s="3" t="s">
+        <v>539</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C220" s="2">
         <v>3</v>
@@ -4958,10 +4965,10 @@
     </row>
     <row r="221" spans="1:4" ht="28.5">
       <c r="A221" s="2" t="s">
-        <v>224</v>
+        <v>567</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2">
@@ -4970,10 +4977,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="2" t="s">
-        <v>225</v>
+        <v>568</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2">
@@ -4982,7 +4989,7 @@
     </row>
     <row r="223" spans="1:4" ht="28.5">
       <c r="A223" s="2" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -4990,10 +4997,10 @@
     </row>
     <row r="224" spans="1:4" ht="28.5">
       <c r="A224" s="2" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2">
@@ -5002,10 +5009,10 @@
     </row>
     <row r="225" spans="1:4" ht="28.5">
       <c r="A225" s="2" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2">
@@ -5014,7 +5021,7 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="2" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -5024,7 +5031,7 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="2" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>5</v>
@@ -5036,27 +5043,27 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="2" t="s">
-        <v>230</v>
+        <v>186</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="2" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="2" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -5064,40 +5071,40 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="2" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="2" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="2" t="s">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="2" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C234" s="2">
         <v>2</v>
@@ -5108,17 +5115,17 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="2" t="s">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="2" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -5126,10 +5133,10 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="2" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2">
@@ -5138,7 +5145,7 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="2" t="s">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>5</v>
@@ -5150,7 +5157,7 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="2" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>5</v>
@@ -5162,7 +5169,7 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="2" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>5</v>
@@ -5174,7 +5181,7 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="2" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>5</v>
@@ -5186,7 +5193,7 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="2" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>5</v>
@@ -5198,7 +5205,7 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="2" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>5</v>
@@ -5208,7 +5215,7 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="2" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>5</v>
@@ -5218,7 +5225,7 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="2" t="s">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>5</v>
@@ -5228,7 +5235,7 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="2" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>5</v>
@@ -5238,7 +5245,7 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="2" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>5</v>
@@ -5248,7 +5255,7 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="2" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>5</v>
@@ -5258,7 +5265,7 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="2" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>5</v>
@@ -5272,7 +5279,7 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="2" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>5</v>
@@ -5282,7 +5289,7 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="2" t="s">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>5</v>
@@ -5292,7 +5299,7 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="2" t="s">
-        <v>254</v>
+        <v>210</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>5</v>
@@ -5302,7 +5309,7 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="2" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>5</v>
@@ -5312,7 +5319,7 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="2" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>5</v>
@@ -5322,30 +5329,30 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="2" t="s">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="2" t="s">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="2" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C257" s="2">
         <v>2</v>
@@ -5356,30 +5363,30 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="2" t="s">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="2" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="2" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C260" s="2">
         <v>2</v>
@@ -5390,10 +5397,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="2" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C261" s="2">
         <v>2</v>
@@ -5404,40 +5411,40 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="2" t="s">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="2" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="2" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="2" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C265" s="2">
         <v>2</v>
@@ -5448,10 +5455,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="2" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2">
@@ -5460,10 +5467,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="2" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2">
@@ -5472,10 +5479,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="2" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C268" s="2">
         <v>2</v>
@@ -5486,60 +5493,60 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="2" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="2" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="2" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="2" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="2" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="2" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2">
@@ -5548,20 +5555,20 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="2" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="2" t="s">
-        <v>278</v>
+        <v>569</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2">
@@ -5570,17 +5577,17 @@
     </row>
     <row r="277" spans="1:4" ht="28.5">
       <c r="A277" s="2" t="s">
-        <v>279</v>
+        <v>570</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="2" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -5588,7 +5595,7 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="2" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -5596,10 +5603,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="2" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2">
@@ -5608,10 +5615,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="2" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2">
@@ -5620,10 +5627,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="2" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2">
@@ -5632,10 +5639,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="2" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2">
@@ -5644,10 +5651,10 @@
     </row>
     <row r="284" spans="1:4" ht="28.5">
       <c r="A284" s="2" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="2">
@@ -5656,7 +5663,7 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="2" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -5666,10 +5673,10 @@
     </row>
     <row r="286" spans="1:4" ht="28.5">
       <c r="A286" s="2" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" s="2">
@@ -5678,10 +5685,10 @@
     </row>
     <row r="287" spans="1:4" ht="28.5">
       <c r="A287" s="2" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" s="2">
@@ -5690,7 +5697,7 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="2" t="s">
-        <v>290</v>
+        <v>614</v>
       </c>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -5698,17 +5705,17 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="2" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="2" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -5716,20 +5723,20 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="2" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="2" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C292" s="2">
         <v>2</v>
@@ -5740,10 +5747,10 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="2" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" s="2">
@@ -5752,10 +5759,10 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="2" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C294" s="2">
         <v>2</v>
@@ -5766,7 +5773,7 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="2" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -5774,17 +5781,17 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="2" t="s">
-        <v>297</v>
+        <v>540</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="2" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -5792,7 +5799,7 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="2" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>5</v>
@@ -5804,7 +5811,7 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="2" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>5</v>
@@ -5816,7 +5823,7 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="2" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>5</v>
@@ -5828,7 +5835,7 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="2" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>5</v>
@@ -5840,7 +5847,7 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" s="2" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>5</v>
@@ -5852,7 +5859,7 @@
     </row>
     <row r="303" spans="1:4" ht="15">
       <c r="A303" s="3" t="s">
-        <v>683</v>
+        <v>518</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>5</v>
@@ -5864,7 +5871,7 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" s="2" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>5</v>
@@ -5876,7 +5883,7 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" s="2" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>5</v>
@@ -5888,7 +5895,7 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" s="2" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>5</v>
@@ -5900,7 +5907,7 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" s="2" t="s">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>5</v>
@@ -5912,7 +5919,7 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" s="2" t="s">
-        <v>308</v>
+        <v>259</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>5</v>
@@ -5924,7 +5931,7 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" s="2" t="s">
-        <v>309</v>
+        <v>260</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>5</v>
@@ -5936,7 +5943,7 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" s="2" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>5</v>
@@ -5948,7 +5955,7 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" s="2" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>5</v>
@@ -5960,7 +5967,7 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" s="2" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>5</v>
@@ -5972,7 +5979,7 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" s="2" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>5</v>
@@ -5984,7 +5991,7 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" s="2" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>5</v>
@@ -5996,7 +6003,7 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" s="2" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>5</v>
@@ -6008,7 +6015,7 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" s="2" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>5</v>
@@ -6020,7 +6027,7 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" s="2" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>5</v>
@@ -6032,7 +6039,7 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" s="2" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>5</v>
@@ -6044,7 +6051,7 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" s="2" t="s">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>5</v>
@@ -6056,7 +6063,7 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" s="2" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>5</v>
@@ -6068,7 +6075,7 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" s="2" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>5</v>
@@ -6080,7 +6087,7 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" s="2" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>5</v>
@@ -6092,10 +6099,10 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" s="2" t="s">
-        <v>323</v>
+        <v>572</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" s="2">
@@ -6104,10 +6111,10 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" s="2" t="s">
-        <v>324</v>
+        <v>573</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="2">
@@ -6116,10 +6123,10 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="2" t="s">
-        <v>325</v>
+        <v>574</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="2">
@@ -6128,10 +6135,10 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" s="2" t="s">
-        <v>326</v>
+        <v>575</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="2">
@@ -6140,10 +6147,10 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" s="2" t="s">
-        <v>327</v>
+        <v>576</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" s="2">
@@ -6152,10 +6159,10 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" s="2" t="s">
-        <v>684</v>
+        <v>577</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" s="2">
@@ -6164,10 +6171,10 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" s="2" t="s">
-        <v>328</v>
+        <v>578</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" s="2">
@@ -6176,10 +6183,10 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" s="2" t="s">
-        <v>329</v>
+        <v>579</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" s="2">
@@ -6188,10 +6195,10 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" s="2" t="s">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="2">
@@ -6200,10 +6207,10 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" s="2" t="s">
-        <v>331</v>
+        <v>581</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" s="2">
@@ -6212,10 +6219,10 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="2" t="s">
-        <v>332</v>
+        <v>582</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" s="2">
@@ -6224,10 +6231,10 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" s="2" t="s">
-        <v>333</v>
+        <v>583</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" s="2">
@@ -6236,10 +6243,10 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" s="2" t="s">
-        <v>334</v>
+        <v>584</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" s="2">
@@ -6248,10 +6255,10 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" s="2" t="s">
-        <v>335</v>
+        <v>585</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" s="2">
@@ -6260,10 +6267,10 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" s="2" t="s">
-        <v>336</v>
+        <v>586</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" s="2">
@@ -6272,10 +6279,10 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" s="2" t="s">
-        <v>337</v>
+        <v>587</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" s="2">
@@ -6284,10 +6291,10 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" s="2" t="s">
-        <v>338</v>
+        <v>588</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" s="2">
@@ -6296,10 +6303,10 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" s="2" t="s">
-        <v>339</v>
+        <v>589</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" s="2">
@@ -6308,10 +6315,10 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" s="2" t="s">
-        <v>340</v>
+        <v>590</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" s="2">
@@ -6320,10 +6327,10 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" s="2" t="s">
-        <v>341</v>
+        <v>591</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" s="2">
@@ -6332,10 +6339,10 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" s="2" t="s">
-        <v>342</v>
+        <v>592</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" s="2">
@@ -6344,10 +6351,10 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" s="2" t="s">
-        <v>343</v>
+        <v>593</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" s="2">
@@ -6356,10 +6363,10 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" s="2" t="s">
-        <v>344</v>
+        <v>594</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="2">
@@ -6368,10 +6375,10 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" s="2" t="s">
-        <v>345</v>
+        <v>595</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" s="2">
@@ -6380,10 +6387,10 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" s="2" t="s">
-        <v>346</v>
+        <v>596</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" s="2">
@@ -6392,10 +6399,10 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" s="2" t="s">
-        <v>347</v>
+        <v>657</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" s="2">
@@ -6404,10 +6411,10 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" s="2" t="s">
-        <v>348</v>
+        <v>658</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" s="2">
@@ -6416,10 +6423,10 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" s="2" t="s">
-        <v>349</v>
+        <v>659</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="2">
@@ -6428,10 +6435,10 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" s="2" t="s">
-        <v>350</v>
+        <v>660</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" s="2">
@@ -6440,10 +6447,10 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" s="2" t="s">
-        <v>351</v>
+        <v>661</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" s="2">
@@ -6452,10 +6459,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" s="2" t="s">
-        <v>685</v>
+        <v>662</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" s="2">
@@ -6464,10 +6471,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" s="2" t="s">
-        <v>352</v>
+        <v>663</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" s="2">
@@ -6476,10 +6483,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" s="2" t="s">
-        <v>353</v>
+        <v>664</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" s="2">
@@ -6488,10 +6495,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" s="2" t="s">
-        <v>354</v>
+        <v>665</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" s="2">
@@ -6500,10 +6507,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" s="2" t="s">
-        <v>355</v>
+        <v>666</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" s="2">
@@ -6512,10 +6519,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" s="2" t="s">
-        <v>356</v>
+        <v>667</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C358" s="2"/>
       <c r="D358" s="2">
@@ -6524,10 +6531,10 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" s="2" t="s">
-        <v>357</v>
+        <v>668</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C359" s="2"/>
       <c r="D359" s="2">
@@ -6536,10 +6543,10 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" s="2" t="s">
-        <v>358</v>
+        <v>669</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C360" s="2"/>
       <c r="D360" s="2">
@@ -6548,10 +6555,10 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" s="2" t="s">
-        <v>359</v>
+        <v>670</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C361" s="2"/>
       <c r="D361" s="2">
@@ -6560,10 +6567,10 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" s="2" t="s">
-        <v>360</v>
+        <v>671</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" s="2">
@@ -6572,10 +6579,10 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" s="2" t="s">
-        <v>361</v>
+        <v>672</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C363" s="2"/>
       <c r="D363" s="2">
@@ -6584,10 +6591,10 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" s="2" t="s">
-        <v>362</v>
+        <v>673</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C364" s="2"/>
       <c r="D364" s="2">
@@ -6596,10 +6603,10 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" s="2" t="s">
-        <v>363</v>
+        <v>674</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" s="2">
@@ -6608,10 +6615,10 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" s="2" t="s">
-        <v>364</v>
+        <v>675</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" s="2">
@@ -6620,10 +6627,10 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" s="2" t="s">
-        <v>365</v>
+        <v>676</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C367" s="2"/>
       <c r="D367" s="2">
@@ -6632,10 +6639,10 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" s="2" t="s">
-        <v>366</v>
+        <v>677</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C368" s="2"/>
       <c r="D368" s="2">
@@ -6644,10 +6651,10 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" s="2" t="s">
-        <v>367</v>
+        <v>678</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" s="2">
@@ -6656,10 +6663,10 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" s="2" t="s">
-        <v>368</v>
+        <v>679</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C370" s="2"/>
       <c r="D370" s="2">
@@ -6668,10 +6675,10 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" s="2" t="s">
-        <v>369</v>
+        <v>680</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C371" s="2"/>
       <c r="D371" s="2">
@@ -6680,10 +6687,10 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" s="2" t="s">
-        <v>370</v>
+        <v>681</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C372" s="2"/>
       <c r="D372" s="2">
@@ -6692,350 +6699,350 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" s="2" t="s">
-        <v>371</v>
+        <v>274</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C373" s="2"/>
       <c r="D373" s="2"/>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C374" s="2"/>
       <c r="D374" s="2"/>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" s="2" t="s">
-        <v>374</v>
+        <v>277</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C375" s="2"/>
       <c r="D375" s="2"/>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" s="2" t="s">
-        <v>375</v>
+        <v>278</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" s="2" t="s">
-        <v>376</v>
+        <v>279</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C377" s="2"/>
       <c r="D377" s="2"/>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" s="2" t="s">
-        <v>377</v>
+        <v>280</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C378" s="2"/>
       <c r="D378" s="2"/>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" s="2" t="s">
-        <v>378</v>
+        <v>281</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" s="2"/>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" s="2" t="s">
-        <v>379</v>
+        <v>282</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="2"/>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" s="2" t="s">
-        <v>380</v>
+        <v>283</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" s="2"/>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" s="2" t="s">
-        <v>381</v>
+        <v>284</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" s="2"/>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" s="2" t="s">
-        <v>382</v>
+        <v>285</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" s="2"/>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" s="2" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" s="2"/>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" s="2" t="s">
-        <v>384</v>
+        <v>287</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" s="2"/>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" s="2" t="s">
-        <v>385</v>
+        <v>288</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" s="2"/>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" s="2" t="s">
-        <v>386</v>
+        <v>289</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" s="2"/>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" s="2" t="s">
-        <v>375</v>
+        <v>278</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" s="2"/>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" s="2" t="s">
-        <v>387</v>
+        <v>290</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" s="2"/>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" s="2" t="s">
-        <v>388</v>
+        <v>291</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" s="2"/>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" s="2" t="s">
-        <v>389</v>
+        <v>292</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" s="2" t="s">
-        <v>390</v>
+        <v>293</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" s="2"/>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" s="2" t="s">
-        <v>391</v>
+        <v>294</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" s="2" t="s">
-        <v>392</v>
+        <v>295</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C394" s="2"/>
       <c r="D394" s="2"/>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" s="2" t="s">
-        <v>393</v>
+        <v>296</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" s="2"/>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" s="2" t="s">
-        <v>394</v>
+        <v>297</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C396" s="2"/>
       <c r="D396" s="2"/>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" s="2" t="s">
-        <v>395</v>
+        <v>298</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C397" s="2"/>
       <c r="D397" s="2"/>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" s="2" t="s">
-        <v>396</v>
+        <v>299</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>372</v>
+        <v>275</v>
       </c>
       <c r="C398" s="2"/>
       <c r="D398" s="2"/>
     </row>
     <row r="399" spans="1:4" ht="42.75">
       <c r="A399" s="2" t="s">
-        <v>397</v>
+        <v>300</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C399" s="2"/>
       <c r="D399" s="2"/>
     </row>
     <row r="400" spans="1:4" ht="42.75">
       <c r="A400" s="2" t="s">
-        <v>399</v>
+        <v>302</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="2"/>
     </row>
     <row r="401" spans="1:4" ht="42.75">
       <c r="A401" s="2" t="s">
-        <v>400</v>
+        <v>303</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" s="2"/>
     </row>
     <row r="402" spans="1:4" ht="42.75">
       <c r="A402" s="2" t="s">
-        <v>401</v>
+        <v>304</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" s="2"/>
     </row>
     <row r="403" spans="1:4" ht="42.75">
       <c r="A403" s="2" t="s">
-        <v>402</v>
+        <v>305</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" s="2"/>
     </row>
     <row r="404" spans="1:4" ht="42.75">
       <c r="A404" s="2" t="s">
-        <v>403</v>
+        <v>306</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="2"/>
     </row>
     <row r="405" spans="1:4" ht="42.75">
       <c r="A405" s="2" t="s">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="2"/>
     </row>
     <row r="406" spans="1:4" ht="42.75">
       <c r="A406" s="2" t="s">
-        <v>405</v>
+        <v>308</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" s="2"/>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" s="2" t="s">
-        <v>406</v>
+        <v>615</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C407" s="2">
         <v>1</v>
@@ -7046,10 +7053,10 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" s="2" t="s">
-        <v>407</v>
+        <v>616</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C408" s="2">
         <v>1</v>
@@ -7060,10 +7067,10 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" s="2" t="s">
-        <v>408</v>
+        <v>617</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C409" s="2">
         <v>1</v>
@@ -7074,10 +7081,10 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" s="2" t="s">
-        <v>409</v>
+        <v>618</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C410" s="2">
         <v>1</v>
@@ -7088,10 +7095,10 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" s="2" t="s">
-        <v>410</v>
+        <v>619</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C411" s="2">
         <v>1</v>
@@ -7102,10 +7109,10 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" s="2" t="s">
-        <v>686</v>
+        <v>620</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C412" s="2">
         <v>1</v>
@@ -7116,10 +7123,10 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" s="2" t="s">
-        <v>411</v>
+        <v>621</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C413" s="2">
         <v>1</v>
@@ -7130,10 +7137,10 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" s="2" t="s">
-        <v>412</v>
+        <v>622</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C414" s="2">
         <v>1</v>
@@ -7144,10 +7151,10 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" s="2" t="s">
-        <v>413</v>
+        <v>623</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C415" s="2">
         <v>1</v>
@@ -7158,10 +7165,10 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" s="2" t="s">
-        <v>414</v>
+        <v>624</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C416" s="2">
         <v>1</v>
@@ -7172,10 +7179,10 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" s="2" t="s">
-        <v>415</v>
+        <v>625</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C417" s="2">
         <v>1</v>
@@ -7186,10 +7193,10 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" s="2" t="s">
-        <v>416</v>
+        <v>626</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C418" s="2">
         <v>1</v>
@@ -7200,10 +7207,10 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" s="2" t="s">
-        <v>417</v>
+        <v>627</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C419" s="2">
         <v>1</v>
@@ -7214,10 +7221,10 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" s="2" t="s">
-        <v>418</v>
+        <v>628</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C420" s="2">
         <v>1</v>
@@ -7228,10 +7235,10 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" s="2" t="s">
-        <v>419</v>
+        <v>629</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C421" s="2">
         <v>1</v>
@@ -7242,10 +7249,10 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" s="2" t="s">
-        <v>420</v>
+        <v>630</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C422" s="2">
         <v>1</v>
@@ -7256,10 +7263,10 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" s="2" t="s">
-        <v>421</v>
+        <v>631</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C423" s="2">
         <v>1</v>
@@ -7270,10 +7277,10 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" s="2" t="s">
-        <v>422</v>
+        <v>632</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C424" s="2">
         <v>1</v>
@@ -7284,10 +7291,10 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" s="2" t="s">
-        <v>423</v>
+        <v>633</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C425" s="2">
         <v>1</v>
@@ -7298,10 +7305,10 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" s="2" t="s">
-        <v>424</v>
+        <v>634</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C426" s="2">
         <v>1</v>
@@ -7312,10 +7319,10 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" s="2" t="s">
-        <v>425</v>
+        <v>635</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C427" s="2">
         <v>1</v>
@@ -7326,10 +7333,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" s="2" t="s">
-        <v>426</v>
+        <v>636</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C428" s="2">
         <v>1</v>
@@ -7340,10 +7347,10 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" s="2" t="s">
-        <v>427</v>
+        <v>637</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C429" s="2">
         <v>1</v>
@@ -7354,10 +7361,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" s="2" t="s">
-        <v>428</v>
+        <v>638</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C430" s="2">
         <v>1</v>
@@ -7368,10 +7375,10 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" s="2" t="s">
-        <v>429</v>
+        <v>639</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C431" s="2">
         <v>1</v>
@@ -7382,10 +7389,10 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" s="2" t="s">
-        <v>430</v>
+        <v>640</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C432" s="2">
         <v>1</v>
@@ -7396,10 +7403,10 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" s="2" t="s">
-        <v>431</v>
+        <v>641</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C433" s="2">
         <v>1</v>
@@ -7410,10 +7417,10 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" s="2" t="s">
-        <v>432</v>
+        <v>642</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C434" s="2">
         <v>1</v>
@@ -7424,10 +7431,10 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" s="2" t="s">
-        <v>433</v>
+        <v>643</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C435" s="2">
         <v>1</v>
@@ -7438,10 +7445,10 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" s="2" t="s">
-        <v>434</v>
+        <v>644</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C436" s="2">
         <v>1</v>
@@ -7452,10 +7459,10 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" s="2" t="s">
-        <v>435</v>
+        <v>645</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C437" s="2">
         <v>1</v>
@@ -7466,10 +7473,10 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" s="2" t="s">
-        <v>436</v>
+        <v>646</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C438" s="2">
         <v>1</v>
@@ -7480,10 +7487,10 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" s="2" t="s">
-        <v>437</v>
+        <v>647</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C439" s="2">
         <v>1</v>
@@ -7494,7 +7501,7 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" s="2" t="s">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>5</v>
@@ -7504,7 +7511,7 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" s="2" t="s">
-        <v>439</v>
+        <v>682</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>5</v>
@@ -7514,7 +7521,7 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" s="2" t="s">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>5</v>
@@ -7524,7 +7531,7 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" s="2" t="s">
-        <v>441</v>
+        <v>311</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>5</v>
@@ -7534,10 +7541,10 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" s="2" t="s">
-        <v>442</v>
+        <v>312</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C444" s="2"/>
       <c r="D444" s="2">
@@ -7546,10 +7553,10 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" s="2" t="s">
-        <v>443</v>
+        <v>313</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C445" s="2"/>
       <c r="D445" s="2">
@@ -7558,10 +7565,10 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" s="2" t="s">
-        <v>444</v>
+        <v>541</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C446" s="2">
         <v>2</v>
@@ -7572,10 +7579,10 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" s="2" t="s">
-        <v>445</v>
+        <v>314</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C447" s="2">
         <v>2</v>
@@ -7586,10 +7593,10 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" s="2" t="s">
-        <v>446</v>
+        <v>542</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C448" s="2"/>
       <c r="D448" s="2">
@@ -7598,10 +7605,10 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" s="2" t="s">
-        <v>447</v>
+        <v>315</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C449" s="2"/>
       <c r="D449" s="2">
@@ -7610,10 +7617,10 @@
     </row>
     <row r="450" spans="1:4" ht="28.5">
       <c r="A450" s="2" t="s">
-        <v>448</v>
+        <v>316</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C450" s="2"/>
       <c r="D450" s="2">
@@ -7622,10 +7629,10 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" s="2" t="s">
-        <v>449</v>
+        <v>597</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C451" s="2"/>
       <c r="D451" s="2">
@@ -7634,60 +7641,60 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" s="2" t="s">
-        <v>450</v>
+        <v>317</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C452" s="2"/>
       <c r="D452" s="2"/>
     </row>
     <row r="453" spans="1:4">
       <c r="A453" s="2" t="s">
-        <v>451</v>
+        <v>318</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C453" s="2"/>
       <c r="D453" s="2"/>
     </row>
     <row r="454" spans="1:4">
       <c r="A454" s="2" t="s">
-        <v>452</v>
+        <v>319</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C454" s="2"/>
       <c r="D454" s="2"/>
     </row>
     <row r="455" spans="1:4">
       <c r="A455" s="2" t="s">
-        <v>453</v>
+        <v>320</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C455" s="2"/>
       <c r="D455" s="2"/>
     </row>
     <row r="456" spans="1:4">
       <c r="A456" s="2" t="s">
-        <v>454</v>
+        <v>598</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C456" s="2"/>
       <c r="D456" s="2"/>
     </row>
     <row r="457" spans="1:4">
       <c r="A457" s="2" t="s">
-        <v>455</v>
+        <v>321</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C457" s="2">
         <v>2</v>
@@ -7698,10 +7705,10 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" s="2" t="s">
-        <v>456</v>
+        <v>322</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C458" s="2">
         <v>2</v>
@@ -7712,20 +7719,20 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" s="2" t="s">
-        <v>457</v>
+        <v>323</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C459" s="2"/>
       <c r="D459" s="2"/>
     </row>
     <row r="460" spans="1:4">
       <c r="A460" s="2" t="s">
-        <v>458</v>
+        <v>324</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C460" s="2"/>
       <c r="D460" s="2">
@@ -7734,20 +7741,20 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" s="2" t="s">
-        <v>459</v>
+        <v>325</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C461" s="2"/>
       <c r="D461" s="2"/>
     </row>
     <row r="462" spans="1:4">
       <c r="A462" s="2" t="s">
-        <v>460</v>
+        <v>326</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C462" s="2">
         <v>2</v>
@@ -7758,40 +7765,40 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" s="2" t="s">
-        <v>461</v>
+        <v>327</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C463" s="2"/>
       <c r="D463" s="2"/>
     </row>
     <row r="464" spans="1:4">
       <c r="A464" s="2" t="s">
-        <v>462</v>
+        <v>328</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C464" s="2"/>
       <c r="D464" s="2"/>
     </row>
     <row r="465" spans="1:4">
       <c r="A465" s="2" t="s">
-        <v>463</v>
+        <v>329</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C465" s="2"/>
       <c r="D465" s="2"/>
     </row>
     <row r="466" spans="1:4">
       <c r="A466" s="2" t="s">
-        <v>464</v>
+        <v>330</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C466" s="2">
         <v>2</v>
@@ -7802,10 +7809,10 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" s="2" t="s">
-        <v>465</v>
+        <v>331</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C467" s="2">
         <v>2</v>
@@ -7816,20 +7823,20 @@
     </row>
     <row r="468" spans="1:4">
       <c r="A468" s="2" t="s">
-        <v>466</v>
+        <v>332</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C468" s="2"/>
       <c r="D468" s="2"/>
     </row>
     <row r="469" spans="1:4">
       <c r="A469" s="2" t="s">
-        <v>467</v>
+        <v>333</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C469" s="2">
         <v>2</v>
@@ -7840,20 +7847,20 @@
     </row>
     <row r="470" spans="1:4">
       <c r="A470" s="2" t="s">
-        <v>468</v>
+        <v>334</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C470" s="2"/>
       <c r="D470" s="2"/>
     </row>
     <row r="471" spans="1:4">
       <c r="A471" s="2" t="s">
-        <v>469</v>
+        <v>335</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C471" s="2">
         <v>2</v>
@@ -7864,20 +7871,20 @@
     </row>
     <row r="472" spans="1:4">
       <c r="A472" s="2" t="s">
-        <v>470</v>
+        <v>336</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C472" s="2"/>
       <c r="D472" s="2"/>
     </row>
     <row r="473" spans="1:4">
       <c r="A473" s="2" t="s">
-        <v>471</v>
+        <v>337</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C473" s="2">
         <v>2</v>
@@ -7888,27 +7895,27 @@
     </row>
     <row r="474" spans="1:4" ht="42.75">
       <c r="A474" s="2" t="s">
-        <v>472</v>
+        <v>338</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C474" s="2"/>
       <c r="D474" s="2"/>
     </row>
     <row r="475" spans="1:4" ht="42.75">
       <c r="A475" s="2" t="s">
-        <v>473</v>
+        <v>339</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="C475" s="2"/>
       <c r="D475" s="2"/>
     </row>
     <row r="476" spans="1:4">
       <c r="A476" s="2" t="s">
-        <v>474</v>
+        <v>340</v>
       </c>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -7916,23 +7923,23 @@
     </row>
     <row r="477" spans="1:4">
       <c r="A477" s="2" t="s">
-        <v>475</v>
+        <v>341</v>
       </c>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
       <c r="D477" s="2"/>
     </row>
-    <row r="478" spans="1:4">
-      <c r="A478" s="2" t="s">
-        <v>476</v>
+    <row r="478" spans="1:4" ht="15">
+      <c r="A478" s="3" t="s">
+        <v>544</v>
       </c>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
       <c r="D478" s="2"/>
     </row>
-    <row r="479" spans="1:4">
-      <c r="A479" s="2" t="s">
-        <v>477</v>
+    <row r="479" spans="1:4" ht="15">
+      <c r="A479" s="3" t="s">
+        <v>545</v>
       </c>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -7940,7 +7947,7 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480" s="2" t="s">
-        <v>478</v>
+        <v>342</v>
       </c>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -7948,7 +7955,7 @@
     </row>
     <row r="481" spans="1:4">
       <c r="A481" s="2" t="s">
-        <v>479</v>
+        <v>343</v>
       </c>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -7956,7 +7963,7 @@
     </row>
     <row r="482" spans="1:4">
       <c r="A482" s="2" t="s">
-        <v>480</v>
+        <v>344</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>5</v>
@@ -7968,7 +7975,7 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483" s="2" t="s">
-        <v>481</v>
+        <v>345</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>5</v>
@@ -7982,7 +7989,7 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="2" t="s">
-        <v>482</v>
+        <v>346</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>5</v>
@@ -7994,7 +8001,7 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="2" t="s">
-        <v>483</v>
+        <v>347</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>5</v>
@@ -8008,7 +8015,7 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="2" t="s">
-        <v>484</v>
+        <v>348</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>5</v>
@@ -8020,7 +8027,7 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="2" t="s">
-        <v>485</v>
+        <v>349</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>5</v>
@@ -8034,7 +8041,7 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="2" t="s">
-        <v>486</v>
+        <v>350</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>5</v>
@@ -8046,7 +8053,7 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="2" t="s">
-        <v>487</v>
+        <v>351</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>5</v>
@@ -8060,7 +8067,7 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="2" t="s">
-        <v>488</v>
+        <v>352</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>5</v>
@@ -8072,7 +8079,7 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="2" t="s">
-        <v>489</v>
+        <v>353</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>5</v>
@@ -8086,7 +8093,7 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="2" t="s">
-        <v>490</v>
+        <v>354</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>5</v>
@@ -8098,7 +8105,7 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="2" t="s">
-        <v>491</v>
+        <v>355</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>5</v>
@@ -8110,7 +8117,7 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="2" t="s">
-        <v>492</v>
+        <v>356</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>5</v>
@@ -8122,7 +8129,7 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="2" t="s">
-        <v>493</v>
+        <v>357</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>5</v>
@@ -8134,7 +8141,7 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="2" t="s">
-        <v>494</v>
+        <v>358</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>5</v>
@@ -8146,7 +8153,7 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="2" t="s">
-        <v>495</v>
+        <v>359</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>5</v>
@@ -8158,7 +8165,7 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="2" t="s">
-        <v>496</v>
+        <v>360</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>5</v>
@@ -8170,7 +8177,7 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="2" t="s">
-        <v>497</v>
+        <v>361</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>5</v>
@@ -8182,7 +8189,7 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="2" t="s">
-        <v>498</v>
+        <v>362</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>5</v>
@@ -8194,7 +8201,7 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="2" t="s">
-        <v>499</v>
+        <v>363</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>5</v>
@@ -8206,7 +8213,7 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="2" t="s">
-        <v>500</v>
+        <v>364</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>5</v>
@@ -8218,7 +8225,7 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="2" t="s">
-        <v>501</v>
+        <v>365</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>5</v>
@@ -8230,7 +8237,7 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="2" t="s">
-        <v>502</v>
+        <v>366</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>5</v>
@@ -8242,7 +8249,7 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="2" t="s">
-        <v>503</v>
+        <v>367</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>5</v>
@@ -8254,7 +8261,7 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="2" t="s">
-        <v>504</v>
+        <v>368</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>5</v>
@@ -8266,7 +8273,7 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="2" t="s">
-        <v>505</v>
+        <v>369</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>5</v>
@@ -8278,7 +8285,7 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="2" t="s">
-        <v>506</v>
+        <v>370</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>5</v>
@@ -8290,7 +8297,7 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="2" t="s">
-        <v>507</v>
+        <v>371</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>5</v>
@@ -8302,7 +8309,7 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="2" t="s">
-        <v>508</v>
+        <v>372</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>5</v>
@@ -8314,7 +8321,7 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="2" t="s">
-        <v>509</v>
+        <v>373</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>5</v>
@@ -8326,7 +8333,7 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="2" t="s">
-        <v>510</v>
+        <v>374</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>5</v>
@@ -8338,7 +8345,7 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="2" t="s">
-        <v>511</v>
+        <v>375</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>5</v>
@@ -8350,10 +8357,10 @@
     </row>
     <row r="514" spans="1:4" ht="28.5">
       <c r="A514" s="2" t="s">
-        <v>512</v>
+        <v>648</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C514" s="2"/>
       <c r="D514" s="2">
@@ -8362,10 +8369,10 @@
     </row>
     <row r="515" spans="1:4" ht="28.5">
       <c r="A515" s="2" t="s">
-        <v>513</v>
+        <v>649</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C515" s="2"/>
       <c r="D515" s="2">
@@ -8374,7 +8381,7 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="2" t="s">
-        <v>514</v>
+        <v>376</v>
       </c>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -8382,7 +8389,7 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="2" t="s">
-        <v>515</v>
+        <v>377</v>
       </c>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -8390,7 +8397,7 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="2" t="s">
-        <v>516</v>
+        <v>378</v>
       </c>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
@@ -8398,7 +8405,7 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="2" t="s">
-        <v>517</v>
+        <v>379</v>
       </c>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -8406,7 +8413,7 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="2" t="s">
-        <v>518</v>
+        <v>599</v>
       </c>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -8414,7 +8421,7 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="2" t="s">
-        <v>519</v>
+        <v>600</v>
       </c>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -8422,10 +8429,10 @@
     </row>
     <row r="522" spans="1:4" ht="28.5">
       <c r="A522" s="2" t="s">
-        <v>520</v>
+        <v>601</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C522" s="2"/>
       <c r="D522" s="2">
@@ -8434,7 +8441,7 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="2" t="s">
-        <v>521</v>
+        <v>602</v>
       </c>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -8442,10 +8449,10 @@
     </row>
     <row r="524" spans="1:4" ht="28.5">
       <c r="A524" s="2" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C524" s="2">
         <v>3</v>
@@ -8456,18 +8463,18 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="2" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
       <c r="D525" s="2"/>
     </row>
     <row r="526" spans="1:4" ht="28.5">
-      <c r="A526" s="2" t="s">
-        <v>524</v>
+      <c r="A526" s="3" t="s">
+        <v>519</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C526" s="2">
         <v>3</v>
@@ -8476,9 +8483,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="527" spans="1:4">
-      <c r="A527" s="2" t="s">
-        <v>525</v>
+    <row r="527" spans="1:4" ht="15">
+      <c r="A527" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
@@ -8486,10 +8493,10 @@
     </row>
     <row r="528" spans="1:4" ht="28.5">
       <c r="A528" s="2" t="s">
-        <v>526</v>
+        <v>380</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C528" s="2"/>
       <c r="D528" s="2">
@@ -8498,10 +8505,10 @@
     </row>
     <row r="529" spans="1:4" ht="28.5">
       <c r="A529" s="2" t="s">
-        <v>527</v>
+        <v>381</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C529" s="2"/>
       <c r="D529" s="2">
@@ -8510,7 +8517,7 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="2" t="s">
-        <v>528</v>
+        <v>382</v>
       </c>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
@@ -8518,7 +8525,7 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="2" t="s">
-        <v>529</v>
+        <v>383</v>
       </c>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -8526,7 +8533,7 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="2" t="s">
-        <v>530</v>
+        <v>384</v>
       </c>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -8534,7 +8541,7 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="2" t="s">
-        <v>531</v>
+        <v>385</v>
       </c>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -8542,10 +8549,10 @@
     </row>
     <row r="534" spans="1:4" ht="28.5">
       <c r="A534" s="2" t="s">
-        <v>532</v>
+        <v>386</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C534" s="2"/>
       <c r="D534" s="2">
@@ -8554,7 +8561,7 @@
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="2" t="s">
-        <v>533</v>
+        <v>387</v>
       </c>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -8562,7 +8569,7 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="2" t="s">
-        <v>534</v>
+        <v>388</v>
       </c>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -8570,7 +8577,7 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="2" t="s">
-        <v>535</v>
+        <v>389</v>
       </c>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -8578,7 +8585,7 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="2" t="s">
-        <v>536</v>
+        <v>390</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>5</v>
@@ -8590,7 +8597,7 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="2" t="s">
-        <v>537</v>
+        <v>391</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>5</v>
@@ -8604,7 +8611,7 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="2" t="s">
-        <v>538</v>
+        <v>392</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>5</v>
@@ -8618,7 +8625,7 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="2" t="s">
-        <v>539</v>
+        <v>393</v>
       </c>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
@@ -8626,7 +8633,7 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="2" t="s">
-        <v>540</v>
+        <v>394</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>5</v>
@@ -8638,7 +8645,7 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="2" t="s">
-        <v>541</v>
+        <v>395</v>
       </c>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -8646,7 +8653,7 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="2" t="s">
-        <v>542</v>
+        <v>396</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>5</v>
@@ -8658,7 +8665,7 @@
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="2" t="s">
-        <v>543</v>
+        <v>397</v>
       </c>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -8666,7 +8673,7 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="2" t="s">
-        <v>544</v>
+        <v>398</v>
       </c>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -8674,7 +8681,7 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="2" t="s">
-        <v>545</v>
+        <v>399</v>
       </c>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
@@ -8682,7 +8689,7 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="2" t="s">
-        <v>546</v>
+        <v>400</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>5</v>
@@ -8694,7 +8701,7 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="2" t="s">
-        <v>547</v>
+        <v>401</v>
       </c>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
@@ -8702,10 +8709,10 @@
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="2" t="s">
-        <v>548</v>
+        <v>603</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C550" s="2"/>
       <c r="D550" s="2">
@@ -8714,10 +8721,10 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="2" t="s">
-        <v>549</v>
+        <v>402</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C551" s="2"/>
       <c r="D551" s="2">
@@ -8726,10 +8733,10 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="2" t="s">
-        <v>550</v>
+        <v>403</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C552" s="2"/>
       <c r="D552" s="2">
@@ -8738,10 +8745,10 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="2" t="s">
-        <v>551</v>
+        <v>404</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C553" s="2"/>
       <c r="D553" s="2">
@@ -8749,11 +8756,11 @@
       </c>
     </row>
     <row r="554" spans="1:4" ht="28.5">
-      <c r="A554" s="2" t="s">
-        <v>552</v>
+      <c r="A554" s="3" t="s">
+        <v>521</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C554" s="2">
         <v>3</v>
@@ -8762,9 +8769,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:4">
-      <c r="A555" s="2" t="s">
-        <v>553</v>
+    <row r="555" spans="1:4" ht="15">
+      <c r="A555" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
@@ -8772,17 +8779,17 @@
     </row>
     <row r="556" spans="1:4" ht="28.5">
       <c r="A556" s="2" t="s">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C556" s="2"/>
       <c r="D556" s="2"/>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="2" t="s">
-        <v>555</v>
+        <v>605</v>
       </c>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -8790,10 +8797,10 @@
     </row>
     <row r="558" spans="1:4" ht="28.5">
       <c r="A558" s="2" t="s">
-        <v>556</v>
+        <v>405</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C558" s="2"/>
       <c r="D558" s="2">
@@ -8802,10 +8809,10 @@
     </row>
     <row r="559" spans="1:4" ht="28.5">
       <c r="A559" s="2" t="s">
-        <v>557</v>
+        <v>406</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C559" s="2"/>
       <c r="D559" s="2">
@@ -8814,10 +8821,10 @@
     </row>
     <row r="560" spans="1:4" ht="28.5">
       <c r="A560" s="2" t="s">
-        <v>558</v>
+        <v>407</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C560" s="2"/>
       <c r="D560" s="2">
@@ -8826,10 +8833,10 @@
     </row>
     <row r="561" spans="1:4" ht="28.5">
       <c r="A561" s="2" t="s">
-        <v>559</v>
+        <v>408</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C561" s="2"/>
       <c r="D561" s="2">
@@ -8838,10 +8845,10 @@
     </row>
     <row r="562" spans="1:4" ht="28.5">
       <c r="A562" s="2" t="s">
-        <v>560</v>
+        <v>409</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C562" s="2"/>
       <c r="D562" s="2">
@@ -8850,10 +8857,10 @@
     </row>
     <row r="563" spans="1:4" ht="28.5">
       <c r="A563" s="2" t="s">
-        <v>561</v>
+        <v>410</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C563" s="2"/>
       <c r="D563" s="2">
@@ -8862,10 +8869,10 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C564" s="2">
         <v>2</v>
@@ -8876,10 +8883,10 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="2" t="s">
-        <v>562</v>
+        <v>411</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C565" s="2"/>
       <c r="D565" s="2">
@@ -8888,10 +8895,10 @@
     </row>
     <row r="566" spans="1:4" ht="28.5">
       <c r="A566" s="2" t="s">
-        <v>563</v>
+        <v>412</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C566" s="2">
         <v>2</v>
@@ -8902,10 +8909,10 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="2" t="s">
-        <v>564</v>
+        <v>413</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C567" s="2">
         <v>2</v>
@@ -8916,10 +8923,10 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="2" t="s">
-        <v>565</v>
+        <v>414</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C568" s="2"/>
       <c r="D568" s="2">
@@ -8928,10 +8935,10 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="2" t="s">
-        <v>566</v>
+        <v>683</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C569" s="2">
         <v>2</v>
@@ -8942,10 +8949,10 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="2" t="s">
-        <v>567</v>
+        <v>415</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C570" s="2"/>
       <c r="D570" s="2">
@@ -8954,10 +8961,10 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="2" t="s">
-        <v>568</v>
+        <v>606</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C571" s="2"/>
       <c r="D571" s="2">
@@ -8966,10 +8973,10 @@
     </row>
     <row r="572" spans="1:4" ht="28.5">
       <c r="A572" s="2" t="s">
-        <v>569</v>
+        <v>416</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C572" s="2"/>
       <c r="D572" s="2">
@@ -8978,10 +8985,10 @@
     </row>
     <row r="573" spans="1:4" ht="28.5">
       <c r="A573" s="2" t="s">
-        <v>570</v>
+        <v>417</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C573" s="2"/>
       <c r="D573" s="2">
@@ -8990,7 +8997,7 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="2" t="s">
-        <v>571</v>
+        <v>418</v>
       </c>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -8998,10 +9005,10 @@
     </row>
     <row r="575" spans="1:4" ht="28.5">
       <c r="A575" s="2" t="s">
-        <v>572</v>
+        <v>419</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C575" s="2"/>
       <c r="D575" s="2">
@@ -9010,10 +9017,10 @@
     </row>
     <row r="576" spans="1:4" ht="28.5">
       <c r="A576" s="2" t="s">
-        <v>573</v>
+        <v>420</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C576" s="2"/>
       <c r="D576" s="2">
@@ -9022,7 +9029,7 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="2" t="s">
-        <v>574</v>
+        <v>421</v>
       </c>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -9030,7 +9037,7 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="2" t="s">
-        <v>8</v>
+        <v>550</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>5</v>
@@ -9042,7 +9049,7 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="2" t="s">
-        <v>13</v>
+        <v>651</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>5</v>
@@ -9054,7 +9061,7 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>5</v>
@@ -9066,7 +9073,7 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="2" t="s">
-        <v>575</v>
+        <v>684</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>5</v>
@@ -9078,7 +9085,7 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="2" t="s">
-        <v>576</v>
+        <v>685</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>5</v>
@@ -9090,7 +9097,7 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="2" t="s">
-        <v>577</v>
+        <v>686</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>5</v>
@@ -9102,7 +9109,7 @@
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="2" t="s">
-        <v>578</v>
+        <v>422</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>5</v>
@@ -9114,7 +9121,7 @@
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="2" t="s">
-        <v>579</v>
+        <v>423</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>5</v>
@@ -9126,7 +9133,7 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="2" t="s">
-        <v>580</v>
+        <v>424</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>5</v>
@@ -9140,7 +9147,7 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="2" t="s">
-        <v>581</v>
+        <v>425</v>
       </c>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -9150,7 +9157,7 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="2" t="s">
-        <v>582</v>
+        <v>426</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>5</v>
@@ -9162,7 +9169,7 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="2" t="s">
-        <v>583</v>
+        <v>427</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>5</v>
@@ -9174,7 +9181,7 @@
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="2" t="s">
-        <v>584</v>
+        <v>428</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>5</v>
@@ -9186,7 +9193,7 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="2" t="s">
-        <v>585</v>
+        <v>429</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>5</v>
@@ -9198,7 +9205,7 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="2" t="s">
-        <v>586</v>
+        <v>430</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>5</v>
@@ -9210,7 +9217,7 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="2" t="s">
-        <v>587</v>
+        <v>431</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>5</v>
@@ -9222,7 +9229,7 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="2" t="s">
-        <v>588</v>
+        <v>432</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>5</v>
@@ -9234,7 +9241,7 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="2" t="s">
-        <v>589</v>
+        <v>433</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>5</v>
@@ -9248,7 +9255,7 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="2" t="s">
-        <v>590</v>
+        <v>434</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>5</v>
@@ -9260,7 +9267,7 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="2" t="s">
-        <v>591</v>
+        <v>435</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>5</v>
@@ -9272,7 +9279,7 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="2" t="s">
-        <v>592</v>
+        <v>436</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>5</v>
@@ -9286,7 +9293,7 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="2" t="s">
-        <v>593</v>
+        <v>437</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>5</v>
@@ -9298,7 +9305,7 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="2" t="s">
-        <v>594</v>
+        <v>438</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>5</v>
@@ -9310,7 +9317,7 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="2" t="s">
-        <v>595</v>
+        <v>439</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>5</v>
@@ -9322,7 +9329,7 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="2" t="s">
-        <v>596</v>
+        <v>440</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>5</v>
@@ -9334,7 +9341,7 @@
     </row>
     <row r="603" spans="1:4">
       <c r="A603" s="2" t="s">
-        <v>597</v>
+        <v>441</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>5</v>
@@ -9346,7 +9353,7 @@
     </row>
     <row r="604" spans="1:4">
       <c r="A604" s="2" t="s">
-        <v>598</v>
+        <v>442</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>5</v>
@@ -9358,7 +9365,7 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="2" t="s">
-        <v>599</v>
+        <v>443</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>5</v>
@@ -9370,7 +9377,7 @@
     </row>
     <row r="606" spans="1:4">
       <c r="A606" s="2" t="s">
-        <v>600</v>
+        <v>444</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>5</v>
@@ -9382,7 +9389,7 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="2" t="s">
-        <v>601</v>
+        <v>445</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>5</v>
@@ -9394,7 +9401,7 @@
     </row>
     <row r="608" spans="1:4">
       <c r="A608" s="2" t="s">
-        <v>602</v>
+        <v>446</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>5</v>
@@ -9406,7 +9413,7 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" s="2" t="s">
-        <v>603</v>
+        <v>447</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>5</v>
@@ -9418,7 +9425,7 @@
     </row>
     <row r="610" spans="1:4">
       <c r="A610" s="2" t="s">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>5</v>
@@ -9430,7 +9437,7 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" s="2" t="s">
-        <v>605</v>
+        <v>449</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>5</v>
@@ -9442,7 +9449,7 @@
     </row>
     <row r="612" spans="1:4">
       <c r="A612" s="2" t="s">
-        <v>606</v>
+        <v>450</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>5</v>
@@ -9454,7 +9461,7 @@
     </row>
     <row r="613" spans="1:4">
       <c r="A613" s="2" t="s">
-        <v>607</v>
+        <v>451</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>5</v>
@@ -9466,7 +9473,7 @@
     </row>
     <row r="614" spans="1:4">
       <c r="A614" s="2" t="s">
-        <v>608</v>
+        <v>452</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>5</v>
@@ -9478,7 +9485,7 @@
     </row>
     <row r="615" spans="1:4">
       <c r="A615" s="2" t="s">
-        <v>609</v>
+        <v>453</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>5</v>
@@ -9490,7 +9497,7 @@
     </row>
     <row r="616" spans="1:4">
       <c r="A616" s="2" t="s">
-        <v>610</v>
+        <v>454</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>5</v>
@@ -9502,7 +9509,7 @@
     </row>
     <row r="617" spans="1:4">
       <c r="A617" s="2" t="s">
-        <v>611</v>
+        <v>455</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>5</v>
@@ -9514,7 +9521,7 @@
     </row>
     <row r="618" spans="1:4">
       <c r="A618" s="2" t="s">
-        <v>612</v>
+        <v>456</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>5</v>
@@ -9526,7 +9533,7 @@
     </row>
     <row r="619" spans="1:4">
       <c r="A619" s="2" t="s">
-        <v>613</v>
+        <v>457</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>5</v>
@@ -9538,7 +9545,7 @@
     </row>
     <row r="620" spans="1:4">
       <c r="A620" s="2" t="s">
-        <v>614</v>
+        <v>458</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>5</v>
@@ -9550,7 +9557,7 @@
     </row>
     <row r="621" spans="1:4">
       <c r="A621" s="2" t="s">
-        <v>615</v>
+        <v>459</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>5</v>
@@ -9562,7 +9569,7 @@
     </row>
     <row r="622" spans="1:4">
       <c r="A622" s="2" t="s">
-        <v>616</v>
+        <v>460</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>5</v>
@@ -9574,7 +9581,7 @@
     </row>
     <row r="623" spans="1:4">
       <c r="A623" s="2" t="s">
-        <v>617</v>
+        <v>461</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>5</v>
@@ -9586,7 +9593,7 @@
     </row>
     <row r="624" spans="1:4">
       <c r="A624" s="2" t="s">
-        <v>618</v>
+        <v>462</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>5</v>
@@ -9598,7 +9605,7 @@
     </row>
     <row r="625" spans="1:4">
       <c r="A625" s="2" t="s">
-        <v>619</v>
+        <v>463</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>5</v>
@@ -9610,7 +9617,7 @@
     </row>
     <row r="626" spans="1:4">
       <c r="A626" s="2" t="s">
-        <v>620</v>
+        <v>464</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>5</v>
@@ -9622,7 +9629,7 @@
     </row>
     <row r="627" spans="1:4">
       <c r="A627" s="2" t="s">
-        <v>621</v>
+        <v>465</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>5</v>
@@ -9634,10 +9641,10 @@
     </row>
     <row r="628" spans="1:4">
       <c r="A628" s="2" t="s">
-        <v>406</v>
+        <v>615</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C628" s="2">
         <v>1</v>
@@ -9648,10 +9655,10 @@
     </row>
     <row r="629" spans="1:4">
       <c r="A629" s="2" t="s">
-        <v>407</v>
+        <v>616</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C629" s="2">
         <v>1</v>
@@ -9662,10 +9669,10 @@
     </row>
     <row r="630" spans="1:4">
       <c r="A630" s="2" t="s">
-        <v>408</v>
+        <v>617</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C630" s="2">
         <v>1</v>
@@ -9676,10 +9683,10 @@
     </row>
     <row r="631" spans="1:4">
       <c r="A631" s="2" t="s">
-        <v>409</v>
+        <v>618</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C631" s="2">
         <v>1</v>
@@ -9690,10 +9697,10 @@
     </row>
     <row r="632" spans="1:4">
       <c r="A632" s="2" t="s">
-        <v>410</v>
+        <v>619</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C632" s="2">
         <v>1</v>
@@ -9704,10 +9711,10 @@
     </row>
     <row r="633" spans="1:4">
       <c r="A633" s="2" t="s">
-        <v>686</v>
+        <v>620</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C633" s="2">
         <v>1</v>
@@ -9718,10 +9725,10 @@
     </row>
     <row r="634" spans="1:4">
       <c r="A634" s="2" t="s">
-        <v>411</v>
+        <v>621</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C634" s="2">
         <v>1</v>
@@ -9732,10 +9739,10 @@
     </row>
     <row r="635" spans="1:4">
       <c r="A635" s="2" t="s">
-        <v>412</v>
+        <v>622</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C635" s="2">
         <v>1</v>
@@ -9746,10 +9753,10 @@
     </row>
     <row r="636" spans="1:4">
       <c r="A636" s="2" t="s">
-        <v>413</v>
+        <v>623</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C636" s="2">
         <v>1</v>
@@ -9760,10 +9767,10 @@
     </row>
     <row r="637" spans="1:4">
       <c r="A637" s="2" t="s">
-        <v>414</v>
+        <v>624</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C637" s="2">
         <v>1</v>
@@ -9774,10 +9781,10 @@
     </row>
     <row r="638" spans="1:4">
       <c r="A638" s="2" t="s">
-        <v>415</v>
+        <v>625</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C638" s="2">
         <v>1</v>
@@ -9788,10 +9795,10 @@
     </row>
     <row r="639" spans="1:4">
       <c r="A639" s="2" t="s">
-        <v>416</v>
+        <v>626</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C639" s="2">
         <v>1</v>
@@ -9802,10 +9809,10 @@
     </row>
     <row r="640" spans="1:4">
       <c r="A640" s="2" t="s">
-        <v>417</v>
+        <v>627</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C640" s="2">
         <v>1</v>
@@ -9816,10 +9823,10 @@
     </row>
     <row r="641" spans="1:4">
       <c r="A641" s="2" t="s">
-        <v>418</v>
+        <v>628</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C641" s="2">
         <v>1</v>
@@ -9830,10 +9837,10 @@
     </row>
     <row r="642" spans="1:4">
       <c r="A642" s="2" t="s">
-        <v>419</v>
+        <v>629</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C642" s="2">
         <v>1</v>
@@ -9844,10 +9851,10 @@
     </row>
     <row r="643" spans="1:4">
       <c r="A643" s="2" t="s">
-        <v>420</v>
+        <v>630</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C643" s="2">
         <v>1</v>
@@ -9858,10 +9865,10 @@
     </row>
     <row r="644" spans="1:4">
       <c r="A644" s="2" t="s">
-        <v>421</v>
+        <v>631</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C644" s="2">
         <v>1</v>
@@ -9872,10 +9879,10 @@
     </row>
     <row r="645" spans="1:4">
       <c r="A645" s="2" t="s">
-        <v>422</v>
+        <v>632</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C645" s="2">
         <v>1</v>
@@ -9886,10 +9893,10 @@
     </row>
     <row r="646" spans="1:4">
       <c r="A646" s="2" t="s">
-        <v>423</v>
+        <v>633</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C646" s="2">
         <v>1</v>
@@ -9900,10 +9907,10 @@
     </row>
     <row r="647" spans="1:4">
       <c r="A647" s="2" t="s">
-        <v>424</v>
+        <v>634</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C647" s="2">
         <v>1</v>
@@ -9914,10 +9921,10 @@
     </row>
     <row r="648" spans="1:4">
       <c r="A648" s="2" t="s">
-        <v>425</v>
+        <v>635</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C648" s="2">
         <v>1</v>
@@ -9928,10 +9935,10 @@
     </row>
     <row r="649" spans="1:4">
       <c r="A649" s="2" t="s">
-        <v>426</v>
+        <v>636</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C649" s="2">
         <v>1</v>
@@ -9942,10 +9949,10 @@
     </row>
     <row r="650" spans="1:4">
       <c r="A650" s="2" t="s">
-        <v>427</v>
+        <v>637</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C650" s="2">
         <v>1</v>
@@ -9956,10 +9963,10 @@
     </row>
     <row r="651" spans="1:4">
       <c r="A651" s="2" t="s">
-        <v>428</v>
+        <v>638</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C651" s="2">
         <v>1</v>
@@ -9970,10 +9977,10 @@
     </row>
     <row r="652" spans="1:4">
       <c r="A652" s="2" t="s">
-        <v>429</v>
+        <v>639</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C652" s="2">
         <v>1</v>
@@ -9984,10 +9991,10 @@
     </row>
     <row r="653" spans="1:4">
       <c r="A653" s="2" t="s">
-        <v>430</v>
+        <v>640</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C653" s="2">
         <v>1</v>
@@ -9998,10 +10005,10 @@
     </row>
     <row r="654" spans="1:4">
       <c r="A654" s="2" t="s">
-        <v>431</v>
+        <v>641</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C654" s="2">
         <v>1</v>
@@ -10012,10 +10019,10 @@
     </row>
     <row r="655" spans="1:4">
       <c r="A655" s="2" t="s">
-        <v>432</v>
+        <v>642</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C655" s="2">
         <v>1</v>
@@ -10026,10 +10033,10 @@
     </row>
     <row r="656" spans="1:4">
       <c r="A656" s="2" t="s">
-        <v>433</v>
+        <v>643</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C656" s="2">
         <v>1</v>
@@ -10040,10 +10047,10 @@
     </row>
     <row r="657" spans="1:4">
       <c r="A657" s="2" t="s">
-        <v>434</v>
+        <v>644</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C657" s="2">
         <v>1</v>
@@ -10054,10 +10061,10 @@
     </row>
     <row r="658" spans="1:4">
       <c r="A658" s="2" t="s">
-        <v>435</v>
+        <v>645</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C658" s="2">
         <v>1</v>
@@ -10068,10 +10075,10 @@
     </row>
     <row r="659" spans="1:4">
       <c r="A659" s="2" t="s">
-        <v>436</v>
+        <v>646</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C659" s="2">
         <v>1</v>
@@ -10082,10 +10089,10 @@
     </row>
     <row r="660" spans="1:4">
       <c r="A660" s="2" t="s">
-        <v>437</v>
+        <v>647</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C660" s="2">
         <v>1</v>
@@ -10096,10 +10103,10 @@
     </row>
     <row r="661" spans="1:4" ht="42.75">
       <c r="A661" s="2" t="s">
-        <v>622</v>
+        <v>466</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C661" s="2"/>
       <c r="D661" s="2">
@@ -10108,10 +10115,10 @@
     </row>
     <row r="662" spans="1:4" ht="42.75">
       <c r="A662" s="2" t="s">
-        <v>624</v>
+        <v>468</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C662" s="2"/>
       <c r="D662" s="2">
@@ -10120,10 +10127,10 @@
     </row>
     <row r="663" spans="1:4" ht="42.75">
       <c r="A663" s="2" t="s">
-        <v>625</v>
+        <v>469</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C663" s="2">
         <v>2</v>
@@ -10134,10 +10141,10 @@
     </row>
     <row r="664" spans="1:4" ht="42.75">
       <c r="A664" s="2" t="s">
-        <v>626</v>
+        <v>470</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C664" s="2">
         <v>2</v>
@@ -10148,10 +10155,10 @@
     </row>
     <row r="665" spans="1:4" ht="42.75">
       <c r="A665" s="2" t="s">
-        <v>627</v>
+        <v>471</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C665" s="2"/>
       <c r="D665" s="2">
@@ -10160,10 +10167,10 @@
     </row>
     <row r="666" spans="1:4" ht="42.75">
       <c r="A666" s="2" t="s">
-        <v>628</v>
+        <v>472</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C666" s="2"/>
       <c r="D666" s="2">
@@ -10172,10 +10179,10 @@
     </row>
     <row r="667" spans="1:4" ht="42.75">
       <c r="A667" s="2" t="s">
-        <v>629</v>
+        <v>473</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C667" s="2"/>
       <c r="D667" s="2">
@@ -10184,10 +10191,10 @@
     </row>
     <row r="668" spans="1:4" ht="42.75">
       <c r="A668" s="2" t="s">
-        <v>630</v>
+        <v>474</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C668" s="2"/>
       <c r="D668" s="2">
@@ -10196,10 +10203,10 @@
     </row>
     <row r="669" spans="1:4" ht="42.75">
       <c r="A669" s="2" t="s">
-        <v>631</v>
+        <v>475</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C669" s="2"/>
       <c r="D669" s="2">
@@ -10208,10 +10215,10 @@
     </row>
     <row r="670" spans="1:4" ht="42.75">
       <c r="A670" s="2" t="s">
-        <v>632</v>
+        <v>476</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C670" s="2"/>
       <c r="D670" s="2">
@@ -10220,10 +10227,10 @@
     </row>
     <row r="671" spans="1:4" ht="42.75">
       <c r="A671" s="2" t="s">
-        <v>633</v>
+        <v>477</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C671" s="2"/>
       <c r="D671" s="2">
@@ -10232,10 +10239,10 @@
     </row>
     <row r="672" spans="1:4" ht="42.75">
       <c r="A672" s="2" t="s">
-        <v>634</v>
+        <v>478</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C672" s="2"/>
       <c r="D672" s="2">
@@ -10244,10 +10251,10 @@
     </row>
     <row r="673" spans="1:4" ht="42.75">
       <c r="A673" s="2" t="s">
-        <v>635</v>
+        <v>479</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C673" s="2"/>
       <c r="D673" s="2">
@@ -10256,10 +10263,10 @@
     </row>
     <row r="674" spans="1:4" ht="42.75">
       <c r="A674" s="2" t="s">
-        <v>636</v>
+        <v>480</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C674" s="2"/>
       <c r="D674" s="2">
@@ -10268,10 +10275,10 @@
     </row>
     <row r="675" spans="1:4" ht="42.75">
       <c r="A675" s="2" t="s">
-        <v>637</v>
+        <v>481</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C675" s="2"/>
       <c r="D675" s="2">
@@ -10280,10 +10287,10 @@
     </row>
     <row r="676" spans="1:4" ht="42.75">
       <c r="A676" s="2" t="s">
-        <v>638</v>
+        <v>482</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>623</v>
+        <v>467</v>
       </c>
       <c r="C676" s="2"/>
       <c r="D676" s="2">
@@ -10292,7 +10299,7 @@
     </row>
     <row r="677" spans="1:4">
       <c r="A677" s="2" t="s">
-        <v>639</v>
+        <v>483</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>5</v>
@@ -10304,7 +10311,7 @@
     </row>
     <row r="678" spans="1:4">
       <c r="A678" s="2" t="s">
-        <v>640</v>
+        <v>484</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>5</v>
@@ -10316,7 +10323,7 @@
     </row>
     <row r="679" spans="1:4">
       <c r="A679" s="2" t="s">
-        <v>641</v>
+        <v>485</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>5</v>
@@ -10326,7 +10333,7 @@
     </row>
     <row r="680" spans="1:4">
       <c r="A680" s="2" t="s">
-        <v>642</v>
+        <v>486</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>5</v>
@@ -10338,7 +10345,7 @@
     </row>
     <row r="681" spans="1:4">
       <c r="A681" s="2" t="s">
-        <v>643</v>
+        <v>487</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>5</v>
@@ -10350,7 +10357,7 @@
     </row>
     <row r="682" spans="1:4">
       <c r="A682" s="2" t="s">
-        <v>644</v>
+        <v>488</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>5</v>
@@ -10362,7 +10369,7 @@
     </row>
     <row r="683" spans="1:4">
       <c r="A683" s="2" t="s">
-        <v>645</v>
+        <v>489</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>5</v>
@@ -10374,7 +10381,7 @@
     </row>
     <row r="684" spans="1:4">
       <c r="A684" s="2" t="s">
-        <v>646</v>
+        <v>490</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>5</v>
@@ -10386,7 +10393,7 @@
     </row>
     <row r="685" spans="1:4">
       <c r="A685" s="2" t="s">
-        <v>647</v>
+        <v>491</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>5</v>
@@ -10398,7 +10405,7 @@
     </row>
     <row r="686" spans="1:4">
       <c r="A686" s="2" t="s">
-        <v>648</v>
+        <v>492</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>5</v>
@@ -10410,7 +10417,7 @@
     </row>
     <row r="687" spans="1:4">
       <c r="A687" s="2" t="s">
-        <v>649</v>
+        <v>493</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>5</v>
@@ -10420,7 +10427,7 @@
     </row>
     <row r="688" spans="1:4">
       <c r="A688" s="2" t="s">
-        <v>650</v>
+        <v>494</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>5</v>
@@ -10430,7 +10437,7 @@
     </row>
     <row r="689" spans="1:4">
       <c r="A689" s="2" t="s">
-        <v>651</v>
+        <v>495</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>5</v>
@@ -10440,7 +10447,7 @@
     </row>
     <row r="690" spans="1:4">
       <c r="A690" s="2" t="s">
-        <v>652</v>
+        <v>496</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>5</v>
@@ -10450,7 +10457,7 @@
     </row>
     <row r="691" spans="1:4">
       <c r="A691" s="2" t="s">
-        <v>653</v>
+        <v>497</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>5</v>
@@ -10462,7 +10469,7 @@
     </row>
     <row r="692" spans="1:4">
       <c r="A692" s="2" t="s">
-        <v>654</v>
+        <v>498</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>5</v>
@@ -10474,7 +10481,7 @@
     </row>
     <row r="693" spans="1:4">
       <c r="A693" s="2" t="s">
-        <v>655</v>
+        <v>499</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>5</v>
@@ -10482,9 +10489,9 @@
       <c r="C693" s="2"/>
       <c r="D693" s="2"/>
     </row>
-    <row r="694" spans="1:4">
-      <c r="A694" s="2" t="s">
-        <v>656</v>
+    <row r="694" spans="1:4" ht="15">
+      <c r="A694" s="3" t="s">
+        <v>548</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>5</v>
@@ -10494,7 +10501,7 @@
     </row>
     <row r="695" spans="1:4">
       <c r="A695" s="2" t="s">
-        <v>657</v>
+        <v>500</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>5</v>
@@ -10506,7 +10513,7 @@
     </row>
     <row r="696" spans="1:4">
       <c r="A696" s="2" t="s">
-        <v>658</v>
+        <v>501</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>5</v>
@@ -10518,7 +10525,7 @@
     </row>
     <row r="697" spans="1:4">
       <c r="A697" s="2" t="s">
-        <v>659</v>
+        <v>502</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>5</v>
@@ -10530,7 +10537,7 @@
     </row>
     <row r="698" spans="1:4">
       <c r="A698" s="2" t="s">
-        <v>655</v>
+        <v>499</v>
       </c>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
@@ -10540,7 +10547,7 @@
     </row>
     <row r="699" spans="1:4">
       <c r="A699" s="2" t="s">
-        <v>660</v>
+        <v>503</v>
       </c>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
@@ -10548,7 +10555,7 @@
     </row>
     <row r="700" spans="1:4">
       <c r="A700" s="2" t="s">
-        <v>661</v>
+        <v>607</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>5</v>
@@ -10560,7 +10567,7 @@
     </row>
     <row r="701" spans="1:4">
       <c r="A701" s="2" t="s">
-        <v>662</v>
+        <v>504</v>
       </c>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
@@ -10568,7 +10575,7 @@
     </row>
     <row r="702" spans="1:4">
       <c r="A702" s="2" t="s">
-        <v>663</v>
+        <v>505</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>5</v>
@@ -10580,7 +10587,7 @@
     </row>
     <row r="703" spans="1:4">
       <c r="A703" s="2" t="s">
-        <v>664</v>
+        <v>506</v>
       </c>
       <c r="B703" s="2" t="s">
         <v>5</v>
@@ -10592,7 +10599,7 @@
     </row>
     <row r="704" spans="1:4">
       <c r="A704" s="2" t="s">
-        <v>665</v>
+        <v>507</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>5</v>
@@ -10602,7 +10609,7 @@
     </row>
     <row r="705" spans="1:4">
       <c r="A705" s="2" t="s">
-        <v>666</v>
+        <v>508</v>
       </c>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
@@ -10610,7 +10617,7 @@
     </row>
     <row r="706" spans="1:4">
       <c r="A706" s="2" t="s">
-        <v>667</v>
+        <v>509</v>
       </c>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
@@ -10618,7 +10625,7 @@
     </row>
     <row r="707" spans="1:4">
       <c r="A707" s="2" t="s">
-        <v>668</v>
+        <v>608</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>5</v>
@@ -10630,7 +10637,7 @@
     </row>
     <row r="708" spans="1:4">
       <c r="A708" s="2" t="s">
-        <v>669</v>
+        <v>609</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>5</v>
@@ -10642,7 +10649,7 @@
     </row>
     <row r="709" spans="1:4">
       <c r="A709" s="2" t="s">
-        <v>670</v>
+        <v>610</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>5</v>
@@ -10654,7 +10661,7 @@
     </row>
     <row r="710" spans="1:4">
       <c r="A710" s="2" t="s">
-        <v>671</v>
+        <v>611</v>
       </c>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
@@ -10662,7 +10669,7 @@
     </row>
     <row r="711" spans="1:4">
       <c r="A711" s="2" t="s">
-        <v>672</v>
+        <v>510</v>
       </c>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
@@ -10670,7 +10677,7 @@
     </row>
     <row r="712" spans="1:4">
       <c r="A712" s="2" t="s">
-        <v>673</v>
+        <v>612</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>5</v>
@@ -10680,10 +10687,10 @@
     </row>
     <row r="713" spans="1:4">
       <c r="A713" s="2" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C713" s="2">
         <v>2</v>
@@ -10694,10 +10701,10 @@
     </row>
     <row r="714" spans="1:4">
       <c r="A714" s="2" t="s">
-        <v>675</v>
+        <v>549</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C714" s="2"/>
       <c r="D714" s="2">
@@ -10706,10 +10713,10 @@
     </row>
     <row r="715" spans="1:4">
       <c r="A715" s="2" t="s">
-        <v>676</v>
+        <v>511</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C715" s="2">
         <v>2</v>
@@ -10720,10 +10727,10 @@
     </row>
     <row r="716" spans="1:4">
       <c r="A716" s="2" t="s">
-        <v>677</v>
+        <v>512</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C716" s="2">
         <v>2</v>
@@ -10734,10 +10741,10 @@
     </row>
     <row r="717" spans="1:4">
       <c r="A717" s="2" t="s">
-        <v>678</v>
+        <v>513</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C717" s="2"/>
       <c r="D717" s="2">
@@ -10746,10 +10753,10 @@
     </row>
     <row r="718" spans="1:4">
       <c r="A718" s="2" t="s">
-        <v>679</v>
+        <v>514</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C718" s="2">
         <v>2</v>
